--- a/Shear_Wall_Database.xlsx
+++ b/Shear_Wall_Database.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\E2-415\Desktop\Databases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F410B031-A664-462D-8078-B8E990F39624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77618633-1EFE-4AB1-81E0-35F403705773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24435" yWindow="1410" windowWidth="21600" windowHeight="11295" tabRatio="823" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25320" yWindow="270" windowWidth="25440" windowHeight="15270" tabRatio="823" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Database" sheetId="16" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="467">
   <si>
     <t>Author</t>
   </si>
@@ -1340,24 +1340,6 @@
   </si>
   <si>
     <t>HS1O-B</t>
-  </si>
-  <si>
-    <t>N0.5 MG-S</t>
-  </si>
-  <si>
-    <t>H0.5 MG-S</t>
-  </si>
-  <si>
-    <t>H0.5 MG-B</t>
-  </si>
-  <si>
-    <t>N0.5 MG</t>
-  </si>
-  <si>
-    <t>H0.5 MG</t>
-  </si>
-  <si>
-    <t>H0.33OU-F</t>
   </si>
   <si>
     <t>HS1O</t>
@@ -1689,9 +1671,6 @@
     </r>
   </si>
   <si>
-    <t>Park et al. (2018)</t>
-  </si>
-  <si>
     <t>NF2</t>
   </si>
   <si>
@@ -1702,6 +1681,48 @@
   </si>
   <si>
     <t>HF2-600</t>
+  </si>
+  <si>
+    <t>NS0.5M</t>
+  </si>
+  <si>
+    <t>HS0.5M</t>
+  </si>
+  <si>
+    <t>NF0.5M</t>
+  </si>
+  <si>
+    <t>HF0.5M</t>
+  </si>
+  <si>
+    <t>HF0.5M-B</t>
+  </si>
+  <si>
+    <t>NF1M</t>
+  </si>
+  <si>
+    <t>HF1M</t>
+  </si>
+  <si>
+    <t>HF1M-B</t>
+  </si>
+  <si>
+    <t>NF1T-B</t>
+  </si>
+  <si>
+    <t>HF1T-B</t>
+  </si>
+  <si>
+    <t>NS2M</t>
+  </si>
+  <si>
+    <t>HS2M</t>
+  </si>
+  <si>
+    <t>NS2H</t>
+  </si>
+  <si>
+    <t>HS2H</t>
   </si>
 </sst>
 </file>
@@ -1713,7 +1734,7 @@
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1910,12 +1931,6 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="Georgia"/>
-      <family val="1"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -2098,7 +2113,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -2228,17 +2243,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="FF8E8E8E"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF8E8E8E"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2284,7 +2288,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2323,9 +2327,6 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -2706,7 +2707,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M394"/>
+  <dimension ref="A1:N394"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="4" customWidth="1"/>
@@ -2720,9 +2721,9 @@
     <col min="9" max="9" width="10.28515625" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.140625" style="5" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.7109375" style="2"/>
+    <col min="12" max="12" width="8.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.7109375" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.5">
@@ -2736,31 +2737,31 @@
         <v>399</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="J1" s="7" t="s">
         <v>448</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>454</v>
-      </c>
       <c r="K1" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="L1" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="M1" s="6" t="s">
         <v>281</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -2797,11 +2798,11 @@
       <c r="K2" s="10">
         <v>0</v>
       </c>
-      <c r="L2" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M2" s="10">
-        <v>0</v>
+      <c r="L2" s="10">
+        <v>0</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2838,11 +2839,11 @@
       <c r="K3" s="10">
         <v>0.10216773276474768</v>
       </c>
-      <c r="L3" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M3" s="10">
-        <v>0</v>
+      <c r="L3" s="10">
+        <v>0</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2879,11 +2880,11 @@
       <c r="K4" s="10">
         <v>0.20818672296504806</v>
       </c>
-      <c r="L4" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M4" s="10">
-        <v>0</v>
+      <c r="L4" s="10">
+        <v>0</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2920,11 +2921,11 @@
       <c r="K5" s="10">
         <v>0</v>
       </c>
-      <c r="L5" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M5" s="10">
-        <v>0</v>
+      <c r="L5" s="10">
+        <v>0</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2961,11 +2962,11 @@
       <c r="K6" s="10">
         <v>0.10172660288133729</v>
       </c>
-      <c r="L6" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M6" s="10">
-        <v>0</v>
+      <c r="L6" s="10">
+        <v>0</v>
+      </c>
+      <c r="M6" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3002,11 +3003,11 @@
       <c r="K7" s="10">
         <v>0.21184489269595647</v>
       </c>
-      <c r="L7" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M7" s="10">
-        <v>0</v>
+      <c r="L7" s="10">
+        <v>0</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -3043,11 +3044,11 @@
       <c r="K8" s="10">
         <v>0</v>
       </c>
-      <c r="L8" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M8" s="10">
-        <v>0</v>
+      <c r="L8" s="10">
+        <v>0</v>
+      </c>
+      <c r="M8" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -3084,11 +3085,11 @@
       <c r="K9" s="10">
         <v>0</v>
       </c>
-      <c r="L9" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M9" s="10">
-        <v>0</v>
+      <c r="L9" s="10">
+        <v>0</v>
+      </c>
+      <c r="M9" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -3125,11 +3126,11 @@
       <c r="K10" s="10">
         <v>0.10641532380662815</v>
       </c>
-      <c r="L10" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M10" s="10">
-        <v>0</v>
+      <c r="L10" s="10">
+        <v>0</v>
+      </c>
+      <c r="M10" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -3166,11 +3167,11 @@
       <c r="K11" s="10">
         <v>0.21229976975068704</v>
       </c>
-      <c r="L11" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M11" s="10">
-        <v>0</v>
+      <c r="L11" s="10">
+        <v>0</v>
+      </c>
+      <c r="M11" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -3207,11 +3208,11 @@
       <c r="K12" s="10">
         <v>0</v>
       </c>
-      <c r="L12" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M12" s="10">
-        <v>0</v>
+      <c r="L12" s="10">
+        <v>0</v>
+      </c>
+      <c r="M12" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -3248,11 +3249,11 @@
       <c r="K13" s="10">
         <v>0.21367521367521367</v>
       </c>
-      <c r="L13" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M13" s="10">
-        <v>0</v>
+      <c r="L13" s="10">
+        <v>0</v>
+      </c>
+      <c r="M13" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -3289,11 +3290,11 @@
       <c r="K14" s="10">
         <v>0</v>
       </c>
-      <c r="L14" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="10">
-        <v>0</v>
+      <c r="L14" s="10">
+        <v>0</v>
+      </c>
+      <c r="M14" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -3330,11 +3331,11 @@
       <c r="K15" s="10">
         <v>0</v>
       </c>
-      <c r="L15" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M15" s="10">
-        <v>0</v>
+      <c r="L15" s="10">
+        <v>0</v>
+      </c>
+      <c r="M15" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -3371,11 +3372,11 @@
       <c r="K16" s="10">
         <v>0</v>
       </c>
-      <c r="L16" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M16" s="10">
-        <v>0</v>
+      <c r="L16" s="10">
+        <v>0</v>
+      </c>
+      <c r="M16" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:13" s="4" customFormat="1" ht="14.1" customHeight="1">
@@ -3412,11 +3413,11 @@
       <c r="K17" s="10">
         <v>0</v>
       </c>
-      <c r="L17" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M17" s="10">
-        <v>0</v>
+      <c r="L17" s="10">
+        <v>0</v>
+      </c>
+      <c r="M17" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:13" s="4" customFormat="1">
@@ -3453,11 +3454,11 @@
       <c r="K18" s="10">
         <v>0</v>
       </c>
-      <c r="L18" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M18" s="10">
-        <v>0</v>
+      <c r="L18" s="10">
+        <v>0</v>
+      </c>
+      <c r="M18" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -3494,11 +3495,11 @@
       <c r="K19" s="10">
         <v>0</v>
       </c>
-      <c r="L19" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M19" s="10">
-        <v>0</v>
+      <c r="L19" s="10">
+        <v>0</v>
+      </c>
+      <c r="M19" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -3535,11 +3536,11 @@
       <c r="K20" s="10">
         <v>0</v>
       </c>
-      <c r="L20" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M20" s="10">
-        <v>0</v>
+      <c r="L20" s="10">
+        <v>0</v>
+      </c>
+      <c r="M20" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -3576,11 +3577,11 @@
       <c r="K21" s="10">
         <v>0</v>
       </c>
-      <c r="L21" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M21" s="10">
-        <v>0</v>
+      <c r="L21" s="10">
+        <v>0</v>
+      </c>
+      <c r="M21" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -3617,11 +3618,11 @@
       <c r="K22" s="10">
         <v>0</v>
       </c>
-      <c r="L22" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M22" s="10">
-        <v>0</v>
+      <c r="L22" s="10">
+        <v>0</v>
+      </c>
+      <c r="M22" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -3658,11 +3659,11 @@
       <c r="K23" s="10">
         <v>0</v>
       </c>
-      <c r="L23" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M23" s="10">
-        <v>0</v>
+      <c r="L23" s="10">
+        <v>0</v>
+      </c>
+      <c r="M23" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -3699,11 +3700,11 @@
       <c r="K24" s="10">
         <v>0</v>
       </c>
-      <c r="L24" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M24" s="10">
-        <v>0</v>
+      <c r="L24" s="10">
+        <v>0</v>
+      </c>
+      <c r="M24" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -3740,11 +3741,11 @@
       <c r="K25" s="10">
         <v>0</v>
       </c>
-      <c r="L25" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M25" s="10">
-        <v>0</v>
+      <c r="L25" s="10">
+        <v>0</v>
+      </c>
+      <c r="M25" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -3781,11 +3782,11 @@
       <c r="K26" s="10">
         <v>0</v>
       </c>
-      <c r="L26" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M26" s="10">
-        <v>0</v>
+      <c r="L26" s="10">
+        <v>0</v>
+      </c>
+      <c r="M26" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -3822,11 +3823,11 @@
       <c r="K27" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="L27" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M27" s="10">
-        <v>0</v>
+      <c r="L27" s="10">
+        <v>0</v>
+      </c>
+      <c r="M27" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -3863,11 +3864,11 @@
       <c r="K28" s="10">
         <v>0</v>
       </c>
-      <c r="L28" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M28" s="10">
-        <v>0</v>
+      <c r="L28" s="10">
+        <v>0</v>
+      </c>
+      <c r="M28" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -3904,11 +3905,11 @@
       <c r="K29" s="10">
         <v>0</v>
       </c>
-      <c r="L29" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M29" s="10">
-        <v>0</v>
+      <c r="L29" s="10">
+        <v>0</v>
+      </c>
+      <c r="M29" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -3945,11 +3946,11 @@
       <c r="K30" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="L30" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M30" s="10">
-        <v>0</v>
+      <c r="L30" s="10">
+        <v>0</v>
+      </c>
+      <c r="M30" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -3986,11 +3987,11 @@
       <c r="K31" s="10">
         <v>6.9534050179211465E-2</v>
       </c>
-      <c r="L31" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M31" s="10">
-        <v>0</v>
+      <c r="L31" s="10">
+        <v>0</v>
+      </c>
+      <c r="M31" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -4027,11 +4028,11 @@
       <c r="K32" s="10">
         <v>6.9534050179211465E-2</v>
       </c>
-      <c r="L32" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M32" s="10">
-        <v>0</v>
+      <c r="L32" s="10">
+        <v>0</v>
+      </c>
+      <c r="M32" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -4068,11 +4069,11 @@
       <c r="K33" s="10">
         <v>6.9701280227596016E-2</v>
       </c>
-      <c r="L33" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M33" s="10">
-        <v>0</v>
+      <c r="L33" s="10">
+        <v>0</v>
+      </c>
+      <c r="M33" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -4109,11 +4110,11 @@
       <c r="K34" s="10">
         <v>7.2738772928526249E-2</v>
       </c>
-      <c r="L34" s="9" t="s">
+      <c r="L34" s="10">
+        <v>0.17647058823529413</v>
+      </c>
+      <c r="M34" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M34" s="10">
-        <v>0.17647058823529413</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -4150,11 +4151,11 @@
       <c r="K35" s="10">
         <v>7.0137382501807663E-2</v>
       </c>
-      <c r="L35" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M35" s="10">
-        <v>0</v>
+      <c r="L35" s="10">
+        <v>0</v>
+      </c>
+      <c r="M35" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -4191,11 +4192,11 @@
       <c r="K36" s="10">
         <v>6.9701280227596016E-2</v>
       </c>
-      <c r="L36" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M36" s="10">
-        <v>0</v>
+      <c r="L36" s="10">
+        <v>0</v>
+      </c>
+      <c r="M36" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -4232,11 +4233,11 @@
       <c r="K37" s="10">
         <v>6.9534050179211465E-2</v>
       </c>
-      <c r="L37" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M37" s="10">
-        <v>0</v>
+      <c r="L37" s="10">
+        <v>0</v>
+      </c>
+      <c r="M37" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -4273,11 +4274,11 @@
       <c r="K38" s="10">
         <v>6.9534050179211465E-2</v>
       </c>
-      <c r="L38" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M38" s="10">
-        <v>0</v>
+      <c r="L38" s="10">
+        <v>0</v>
+      </c>
+      <c r="M38" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -4314,11 +4315,11 @@
       <c r="K39" s="10">
         <v>0.05</v>
       </c>
-      <c r="L39" s="9" t="s">
+      <c r="L39" s="10">
+        <v>0.30612244897959184</v>
+      </c>
+      <c r="M39" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M39" s="10">
-        <v>0.30612244897959184</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -4355,11 +4356,11 @@
       <c r="K40" s="10">
         <v>0.05</v>
       </c>
-      <c r="L40" s="9" t="s">
+      <c r="L40" s="10">
+        <v>0.30612244897959184</v>
+      </c>
+      <c r="M40" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M40" s="10">
-        <v>0.30612244897959184</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -4396,11 +4397,11 @@
       <c r="K41" s="10">
         <v>0.05</v>
       </c>
-      <c r="L41" s="9" t="s">
+      <c r="L41" s="10">
+        <v>0.30612244897959184</v>
+      </c>
+      <c r="M41" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M41" s="10">
-        <v>0.30612244897959184</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -4437,11 +4438,11 @@
       <c r="K42" s="10">
         <v>0.05</v>
       </c>
-      <c r="L42" s="9" t="s">
+      <c r="L42" s="10">
+        <v>0.30215827338129497</v>
+      </c>
+      <c r="M42" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M42" s="10">
-        <v>0.30215827338129497</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -4478,11 +4479,11 @@
       <c r="K43" s="10">
         <v>0.05</v>
       </c>
-      <c r="L43" s="9" t="s">
+      <c r="L43" s="10">
+        <v>0.30612244897959184</v>
+      </c>
+      <c r="M43" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M43" s="10">
-        <v>0.30612244897959184</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -4519,11 +4520,11 @@
       <c r="K44" s="10">
         <v>0.05</v>
       </c>
-      <c r="L44" s="9" t="s">
+      <c r="L44" s="10">
+        <v>0.30612244897959184</v>
+      </c>
+      <c r="M44" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M44" s="10">
-        <v>0.30612244897959184</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -4560,11 +4561,11 @@
       <c r="K45" s="10">
         <v>0.05</v>
       </c>
-      <c r="L45" s="9" t="s">
+      <c r="L45" s="10">
+        <v>0.30612244897959184</v>
+      </c>
+      <c r="M45" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M45" s="10">
-        <v>0.30612244897959184</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -4601,11 +4602,11 @@
       <c r="K46" s="10">
         <v>0</v>
       </c>
-      <c r="L46" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M46" s="10">
-        <v>0</v>
+      <c r="L46" s="10">
+        <v>0</v>
+      </c>
+      <c r="M46" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -4642,11 +4643,11 @@
       <c r="K47" s="10">
         <v>0</v>
       </c>
-      <c r="L47" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M47" s="10">
-        <v>0</v>
+      <c r="L47" s="10">
+        <v>0</v>
+      </c>
+      <c r="M47" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -4683,11 +4684,11 @@
       <c r="K48" s="10">
         <v>0</v>
       </c>
-      <c r="L48" s="9" t="s">
+      <c r="L48" s="10">
+        <v>0.29240271578550325</v>
+      </c>
+      <c r="M48" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M48" s="10">
-        <v>0.29240271578550325</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -4724,11 +4725,11 @@
       <c r="K49" s="10">
         <v>0</v>
       </c>
-      <c r="L49" s="9" t="s">
+      <c r="L49" s="10">
+        <v>0.29240271578550325</v>
+      </c>
+      <c r="M49" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M49" s="10">
-        <v>0.29240271578550325</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -4765,11 +4766,11 @@
       <c r="K50" s="10">
         <v>0</v>
       </c>
-      <c r="L50" s="9" t="s">
+      <c r="L50" s="10">
+        <v>0.29240271578550325</v>
+      </c>
+      <c r="M50" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M50" s="10">
-        <v>0.29240271578550325</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -4806,11 +4807,11 @@
       <c r="K51" s="10">
         <v>0</v>
       </c>
-      <c r="L51" s="9" t="s">
+      <c r="L51" s="10">
+        <v>0.29240271578550325</v>
+      </c>
+      <c r="M51" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M51" s="10">
-        <v>0.29240271578550325</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -4847,11 +4848,11 @@
       <c r="K52" s="10">
         <v>0</v>
       </c>
-      <c r="L52" s="9" t="s">
+      <c r="L52" s="10">
+        <v>0.29240271578550325</v>
+      </c>
+      <c r="M52" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M52" s="10">
-        <v>0.29240271578550325</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -4888,11 +4889,11 @@
       <c r="K53" s="10">
         <v>0</v>
       </c>
-      <c r="L53" s="9" t="s">
+      <c r="L53" s="10">
+        <v>0.25892351274787534</v>
+      </c>
+      <c r="M53" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M53" s="10">
-        <v>0.25892351274787534</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -4929,11 +4930,11 @@
       <c r="K54" s="10">
         <v>0.1344160409444114</v>
       </c>
-      <c r="L54" s="9" t="s">
+      <c r="L54" s="10">
+        <v>0.29240271578550325</v>
+      </c>
+      <c r="M54" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M54" s="10">
-        <v>0.29240271578550325</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -4970,11 +4971,11 @@
       <c r="K55" s="10">
         <v>7.6219904462436386E-2</v>
       </c>
-      <c r="L55" s="9" t="s">
+      <c r="L55" s="10">
+        <v>0.29240271578550325</v>
+      </c>
+      <c r="M55" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M55" s="10">
-        <v>0.29240271578550325</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -5011,11 +5012,11 @@
       <c r="K56" s="10">
         <v>8.9467649761859863E-2</v>
       </c>
-      <c r="L56" s="9" t="s">
+      <c r="L56" s="10">
+        <v>0.29240271578550325</v>
+      </c>
+      <c r="M56" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M56" s="10">
-        <v>0.29240271578550325</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -5052,11 +5053,11 @@
       <c r="K57" s="10">
         <v>8.5207285487485573E-2</v>
       </c>
-      <c r="L57" s="9" t="s">
+      <c r="L57" s="10">
+        <v>0.29240271578550325</v>
+      </c>
+      <c r="M57" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M57" s="10">
-        <v>0.29240271578550325</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -5093,11 +5094,11 @@
       <c r="K58" s="10">
         <v>8.2404414254344596E-2</v>
       </c>
-      <c r="L58" s="9" t="s">
+      <c r="L58" s="10">
+        <v>0.29240271578550325</v>
+      </c>
+      <c r="M58" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M58" s="10">
-        <v>0.29240271578550325</v>
       </c>
     </row>
     <row r="59" spans="1:13">
@@ -5134,11 +5135,11 @@
       <c r="K59" s="10">
         <v>7.2576354233358759E-2</v>
       </c>
-      <c r="L59" s="9" t="s">
+      <c r="L59" s="10">
+        <v>0.25892351274787534</v>
+      </c>
+      <c r="M59" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M59" s="10">
-        <v>0.25892351274787534</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -5175,11 +5176,11 @@
       <c r="K60" s="10">
         <v>0</v>
       </c>
-      <c r="L60" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M60" s="10">
-        <v>0</v>
+      <c r="L60" s="10">
+        <v>0</v>
+      </c>
+      <c r="M60" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -5216,11 +5217,11 @@
       <c r="K61" s="10">
         <v>0</v>
       </c>
-      <c r="L61" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M61" s="10">
-        <v>0</v>
+      <c r="L61" s="10">
+        <v>0</v>
+      </c>
+      <c r="M61" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:13">
@@ -5257,11 +5258,11 @@
       <c r="K62" s="10">
         <v>0</v>
       </c>
-      <c r="L62" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M62" s="10">
-        <v>0</v>
+      <c r="L62" s="10">
+        <v>0</v>
+      </c>
+      <c r="M62" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="63" spans="1:13">
@@ -5298,11 +5299,11 @@
       <c r="K63" s="10">
         <v>0</v>
       </c>
-      <c r="L63" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M63" s="10">
-        <v>0</v>
+      <c r="L63" s="10">
+        <v>0</v>
+      </c>
+      <c r="M63" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -5339,11 +5340,11 @@
       <c r="K64" s="10">
         <v>0</v>
       </c>
-      <c r="L64" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M64" s="10">
-        <v>0</v>
+      <c r="L64" s="10">
+        <v>0</v>
+      </c>
+      <c r="M64" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -5380,11 +5381,11 @@
       <c r="K65" s="10">
         <v>0.14984358706986445</v>
       </c>
-      <c r="L65" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M65" s="10">
-        <v>0</v>
+      <c r="L65" s="10">
+        <v>0</v>
+      </c>
+      <c r="M65" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -5421,11 +5422,11 @@
       <c r="K66" s="10">
         <v>0.2497393117831074</v>
       </c>
-      <c r="L66" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M66" s="10">
-        <v>0</v>
+      <c r="L66" s="10">
+        <v>0</v>
+      </c>
+      <c r="M66" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -5462,11 +5463,11 @@
       <c r="K67" s="10">
         <v>0.35015641293013555</v>
       </c>
-      <c r="L67" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M67" s="10">
-        <v>0</v>
+      <c r="L67" s="10">
+        <v>0</v>
+      </c>
+      <c r="M67" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -5503,11 +5504,11 @@
       <c r="K68" s="10">
         <v>7.3449666604973526E-2</v>
       </c>
-      <c r="L68" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M68" s="10">
-        <v>0</v>
+      <c r="L68" s="10">
+        <v>0</v>
+      </c>
+      <c r="M68" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="69" spans="1:13">
@@ -5544,11 +5545,11 @@
       <c r="K69" s="10">
         <v>7.3070542346000605E-2</v>
       </c>
-      <c r="L69" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M69" s="10">
-        <v>0</v>
+      <c r="L69" s="10">
+        <v>0</v>
+      </c>
+      <c r="M69" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -5585,11 +5586,11 @@
       <c r="K70" s="10">
         <v>7.7194846339345188E-2</v>
       </c>
-      <c r="L70" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M70" s="10">
-        <v>0</v>
+      <c r="L70" s="10">
+        <v>0</v>
+      </c>
+      <c r="M70" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -5626,11 +5627,11 @@
       <c r="K71" s="10">
         <v>6.4125687740746978E-2</v>
       </c>
-      <c r="L71" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M71" s="10">
-        <v>0</v>
+      <c r="L71" s="10">
+        <v>0</v>
+      </c>
+      <c r="M71" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="72" spans="1:13">
@@ -5667,11 +5668,11 @@
       <c r="K72" s="10">
         <v>1.586249748922007E-2</v>
       </c>
-      <c r="L72" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M72" s="10">
-        <v>0</v>
+      <c r="L72" s="10">
+        <v>0</v>
+      </c>
+      <c r="M72" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -5708,11 +5709,11 @@
       <c r="K73" s="10">
         <v>0</v>
       </c>
-      <c r="L73" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M73" s="10">
-        <v>0</v>
+      <c r="L73" s="10">
+        <v>0</v>
+      </c>
+      <c r="M73" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -5749,11 +5750,11 @@
       <c r="K74" s="10">
         <v>0</v>
       </c>
-      <c r="L74" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M74" s="10">
-        <v>0</v>
+      <c r="L74" s="10">
+        <v>0</v>
+      </c>
+      <c r="M74" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="75" spans="1:13">
@@ -5790,11 +5791,11 @@
       <c r="K75" s="10">
         <v>0</v>
       </c>
-      <c r="L75" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M75" s="10">
-        <v>0</v>
+      <c r="L75" s="10">
+        <v>0</v>
+      </c>
+      <c r="M75" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="76" spans="1:13">
@@ -5831,11 +5832,11 @@
       <c r="K76" s="10">
         <v>0</v>
       </c>
-      <c r="L76" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M76" s="10">
-        <v>0</v>
+      <c r="L76" s="10">
+        <v>0</v>
+      </c>
+      <c r="M76" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -5872,11 +5873,11 @@
       <c r="K77" s="10">
         <v>0</v>
       </c>
-      <c r="L77" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M77" s="10">
-        <v>0</v>
+      <c r="L77" s="10">
+        <v>0</v>
+      </c>
+      <c r="M77" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -5913,11 +5914,11 @@
       <c r="K78" s="10">
         <v>0</v>
       </c>
-      <c r="L78" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M78" s="10">
-        <v>0</v>
+      <c r="L78" s="10">
+        <v>0</v>
+      </c>
+      <c r="M78" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -5954,11 +5955,11 @@
       <c r="K79" s="10">
         <v>0</v>
       </c>
-      <c r="L79" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M79" s="10">
-        <v>0</v>
+      <c r="L79" s="10">
+        <v>0</v>
+      </c>
+      <c r="M79" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -5995,11 +5996,11 @@
       <c r="K80" s="10">
         <v>0</v>
       </c>
-      <c r="L80" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M80" s="10">
-        <v>0</v>
+      <c r="L80" s="10">
+        <v>0</v>
+      </c>
+      <c r="M80" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="81" spans="1:13">
@@ -6036,11 +6037,11 @@
       <c r="K81" s="10">
         <v>0</v>
       </c>
-      <c r="L81" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M81" s="10">
-        <v>0</v>
+      <c r="L81" s="10">
+        <v>0</v>
+      </c>
+      <c r="M81" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="82" spans="1:13">
@@ -6077,11 +6078,11 @@
       <c r="K82" s="10">
         <v>7.5151832253885678E-2</v>
       </c>
-      <c r="L82" s="9" t="s">
+      <c r="L82" s="10">
+        <v>0.38484848484848483</v>
+      </c>
+      <c r="M82" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M82" s="10">
-        <v>0.38484848484848483</v>
       </c>
     </row>
     <row r="83" spans="1:13">
@@ -6118,11 +6119,11 @@
       <c r="K83" s="10">
         <v>6.116079965342823E-2</v>
       </c>
-      <c r="L83" s="9" t="s">
+      <c r="L83" s="10">
+        <v>0.38484848484848483</v>
+      </c>
+      <c r="M83" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M83" s="10">
-        <v>0.38484848484848483</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -6159,11 +6160,11 @@
       <c r="K84" s="10">
         <v>4.3064533089305274E-2</v>
       </c>
-      <c r="L84" s="9" t="s">
+      <c r="L84" s="10">
+        <v>0.38484848484848483</v>
+      </c>
+      <c r="M84" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M84" s="10">
-        <v>0.38484848484848483</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -6200,11 +6201,11 @@
       <c r="K85" s="10">
         <v>2.6372087923955293E-2</v>
       </c>
-      <c r="L85" s="9" t="s">
+      <c r="L85" s="10">
+        <v>0.38484848484848483</v>
+      </c>
+      <c r="M85" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M85" s="10">
-        <v>0.38484848484848483</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -6241,11 +6242,11 @@
       <c r="K86" s="10">
         <v>0</v>
       </c>
-      <c r="L86" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M86" s="10">
-        <v>0</v>
+      <c r="L86" s="10">
+        <v>0</v>
+      </c>
+      <c r="M86" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -6282,11 +6283,11 @@
       <c r="K87" s="10">
         <v>0</v>
       </c>
-      <c r="L87" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M87" s="10">
-        <v>0</v>
+      <c r="L87" s="10">
+        <v>0</v>
+      </c>
+      <c r="M87" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="88" spans="1:13" s="4" customFormat="1">
@@ -6323,11 +6324,11 @@
       <c r="K88" s="10">
         <v>5.3338171262699567E-2</v>
       </c>
-      <c r="L88" s="9" t="s">
+      <c r="L88" s="10">
+        <v>0.23584905660377359</v>
+      </c>
+      <c r="M88" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M88" s="10">
-        <v>0.23584905660377359</v>
       </c>
     </row>
     <row r="89" spans="1:13" s="4" customFormat="1">
@@ -6364,11 +6365,11 @@
       <c r="K89" s="10">
         <v>6.6515837104072398E-2</v>
       </c>
-      <c r="L89" s="9" t="s">
+      <c r="L89" s="10">
+        <v>0.29411764705882354</v>
+      </c>
+      <c r="M89" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M89" s="10">
-        <v>0.29411764705882354</v>
       </c>
     </row>
     <row r="90" spans="1:13" s="4" customFormat="1">
@@ -6405,11 +6406,11 @@
       <c r="K90" s="10">
         <v>0</v>
       </c>
-      <c r="L90" s="9" t="s">
+      <c r="L90" s="10">
+        <v>0.3125</v>
+      </c>
+      <c r="M90" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M90" s="10">
-        <v>0.3125</v>
       </c>
     </row>
     <row r="91" spans="1:13" s="4" customFormat="1">
@@ -6446,11 +6447,11 @@
       <c r="K91" s="10">
         <v>3.6162361623616232E-2</v>
       </c>
-      <c r="L91" s="9" t="s">
+      <c r="L91" s="10">
+        <v>0.3125</v>
+      </c>
+      <c r="M91" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M91" s="10">
-        <v>0.3125</v>
       </c>
     </row>
     <row r="92" spans="1:13" s="4" customFormat="1">
@@ -6487,11 +6488,11 @@
       <c r="K92" s="10">
         <v>7.2862453531598523E-2</v>
       </c>
-      <c r="L92" s="9" t="s">
+      <c r="L92" s="10">
+        <v>0.3125</v>
+      </c>
+      <c r="M92" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M92" s="10">
-        <v>0.3125</v>
       </c>
     </row>
     <row r="93" spans="1:13" s="4" customFormat="1">
@@ -6528,11 +6529,11 @@
       <c r="K93" s="10">
         <v>0.15252918287937742</v>
       </c>
-      <c r="L93" s="9" t="s">
+      <c r="L93" s="10">
+        <v>0.3125</v>
+      </c>
+      <c r="M93" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M93" s="10">
-        <v>0.3125</v>
       </c>
     </row>
     <row r="94" spans="1:13" s="4" customFormat="1">
@@ -6569,11 +6570,11 @@
       <c r="K94" s="10">
         <v>0</v>
       </c>
-      <c r="L94" s="9" t="s">
+      <c r="L94" s="10">
+        <v>0.3125</v>
+      </c>
+      <c r="M94" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M94" s="10">
-        <v>0.3125</v>
       </c>
     </row>
     <row r="95" spans="1:13" s="4" customFormat="1">
@@ -6610,11 +6611,11 @@
       <c r="K95" s="10">
         <v>0</v>
       </c>
-      <c r="L95" s="9" t="s">
+      <c r="L95" s="10">
+        <v>0.3125</v>
+      </c>
+      <c r="M95" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M95" s="10">
-        <v>0.3125</v>
       </c>
     </row>
     <row r="96" spans="1:13" s="4" customFormat="1">
@@ -6651,11 +6652,11 @@
       <c r="K96" s="10">
         <v>6.5551839464882952E-2</v>
       </c>
-      <c r="L96" s="9" t="s">
+      <c r="L96" s="10">
+        <v>0.3125</v>
+      </c>
+      <c r="M96" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M96" s="10">
-        <v>0.3125</v>
       </c>
     </row>
     <row r="97" spans="1:13" s="4" customFormat="1">
@@ -6692,11 +6693,11 @@
       <c r="K97" s="10">
         <v>0</v>
       </c>
-      <c r="L97" s="9" t="s">
+      <c r="L97" s="10">
+        <v>0.22388059701492538</v>
+      </c>
+      <c r="M97" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M97" s="10">
-        <v>0.22388059701492538</v>
       </c>
     </row>
     <row r="98" spans="1:13" s="4" customFormat="1">
@@ -6733,11 +6734,11 @@
       <c r="K98" s="10">
         <v>0</v>
       </c>
-      <c r="L98" s="9" t="s">
+      <c r="L98" s="10">
+        <v>0.22388059701492538</v>
+      </c>
+      <c r="M98" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M98" s="10">
-        <v>0.22388059701492538</v>
       </c>
     </row>
     <row r="99" spans="1:13" s="4" customFormat="1">
@@ -6774,11 +6775,11 @@
       <c r="K99" s="10">
         <v>0</v>
       </c>
-      <c r="L99" s="9" t="s">
+      <c r="L99" s="10">
+        <v>0.22388059701492538</v>
+      </c>
+      <c r="M99" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M99" s="10">
-        <v>0.22388059701492538</v>
       </c>
     </row>
     <row r="100" spans="1:13" s="4" customFormat="1">
@@ -6815,11 +6816,11 @@
       <c r="K100" s="10">
         <v>0</v>
       </c>
-      <c r="L100" s="9" t="s">
+      <c r="L100" s="10">
+        <v>0.22388059701492538</v>
+      </c>
+      <c r="M100" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M100" s="10">
-        <v>0.22388059701492538</v>
       </c>
     </row>
     <row r="101" spans="1:13" s="4" customFormat="1">
@@ -6856,11 +6857,11 @@
       <c r="K101" s="10">
         <v>0</v>
       </c>
-      <c r="L101" s="9" t="s">
+      <c r="L101" s="10">
+        <v>0.22388059701492538</v>
+      </c>
+      <c r="M101" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M101" s="10">
-        <v>0.22388059701492538</v>
       </c>
     </row>
     <row r="102" spans="1:13" s="4" customFormat="1">
@@ -6897,11 +6898,11 @@
       <c r="K102" s="10">
         <v>0</v>
       </c>
-      <c r="L102" s="9" t="s">
+      <c r="L102" s="10">
+        <v>0.22388059701492538</v>
+      </c>
+      <c r="M102" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M102" s="10">
-        <v>0.22388059701492538</v>
       </c>
     </row>
     <row r="103" spans="1:13" s="4" customFormat="1">
@@ -6938,11 +6939,11 @@
       <c r="K103" s="10">
         <v>0</v>
       </c>
-      <c r="L103" s="9" t="s">
+      <c r="L103" s="10">
+        <v>0.22388059701492538</v>
+      </c>
+      <c r="M103" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M103" s="10">
-        <v>0.22388059701492538</v>
       </c>
     </row>
     <row r="104" spans="1:13" s="4" customFormat="1">
@@ -6979,11 +6980,11 @@
       <c r="K104" s="10">
         <v>0</v>
       </c>
-      <c r="L104" s="9" t="s">
+      <c r="L104" s="10">
+        <v>0.24233983286908078</v>
+      </c>
+      <c r="M104" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M104" s="10">
-        <v>0.24233983286908078</v>
       </c>
     </row>
     <row r="105" spans="1:13" s="4" customFormat="1">
@@ -7020,11 +7021,11 @@
       <c r="K105" s="10">
         <v>0</v>
       </c>
-      <c r="L105" s="9" t="s">
+      <c r="L105" s="10">
+        <v>0.25276002324230101</v>
+      </c>
+      <c r="M105" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M105" s="10">
-        <v>0.25276002324230101</v>
       </c>
     </row>
     <row r="106" spans="1:13" s="4" customFormat="1">
@@ -7061,11 +7062,11 @@
       <c r="K106" s="10">
         <v>0</v>
       </c>
-      <c r="L106" s="9" t="s">
+      <c r="L106" s="10">
+        <v>0.24233983286908078</v>
+      </c>
+      <c r="M106" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M106" s="10">
-        <v>0.24233983286908078</v>
       </c>
     </row>
     <row r="107" spans="1:13" s="4" customFormat="1">
@@ -7102,11 +7103,11 @@
       <c r="K107" s="10">
         <v>0</v>
       </c>
-      <c r="L107" s="9" t="s">
+      <c r="L107" s="10">
+        <v>0.27018633540372672</v>
+      </c>
+      <c r="M107" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M107" s="10">
-        <v>0.27018633540372672</v>
       </c>
     </row>
     <row r="108" spans="1:13" s="4" customFormat="1">
@@ -7143,11 +7144,11 @@
       <c r="K108" s="10">
         <v>0</v>
       </c>
-      <c r="L108" s="9" t="s">
+      <c r="L108" s="10">
+        <v>0.25276002324230101</v>
+      </c>
+      <c r="M108" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M108" s="10">
-        <v>0.25276002324230101</v>
       </c>
     </row>
     <row r="109" spans="1:13" s="4" customFormat="1">
@@ -7184,11 +7185,11 @@
       <c r="K109" s="10">
         <v>0</v>
       </c>
-      <c r="L109" s="9" t="s">
+      <c r="L109" s="10">
+        <v>0.24744027303754265</v>
+      </c>
+      <c r="M109" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M109" s="10">
-        <v>0.24744027303754265</v>
       </c>
     </row>
     <row r="110" spans="1:13" s="4" customFormat="1">
@@ -7225,11 +7226,11 @@
       <c r="K110" s="10">
         <v>0</v>
       </c>
-      <c r="L110" s="9" t="s">
+      <c r="L110" s="10">
+        <v>0.25276002324230101</v>
+      </c>
+      <c r="M110" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M110" s="10">
-        <v>0.25276002324230101</v>
       </c>
     </row>
     <row r="111" spans="1:13" s="4" customFormat="1">
@@ -7266,11 +7267,11 @@
       <c r="K111" s="10">
         <v>0</v>
       </c>
-      <c r="L111" s="9" t="s">
+      <c r="L111" s="10">
+        <v>0.24744027303754265</v>
+      </c>
+      <c r="M111" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M111" s="10">
-        <v>0.24744027303754265</v>
       </c>
     </row>
     <row r="112" spans="1:13" s="4" customFormat="1">
@@ -7307,11 +7308,11 @@
       <c r="K112" s="10">
         <v>0</v>
       </c>
-      <c r="L112" s="9" t="s">
+      <c r="L112" s="10">
+        <v>0.23274478330658105</v>
+      </c>
+      <c r="M112" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M112" s="10">
-        <v>0.23274478330658105</v>
       </c>
     </row>
     <row r="113" spans="1:13" s="4" customFormat="1">
@@ -7348,11 +7349,11 @@
       <c r="K113" s="10">
         <v>0</v>
       </c>
-      <c r="L113" s="9" t="s">
+      <c r="L113" s="10">
+        <v>0.24744027303754265</v>
+      </c>
+      <c r="M113" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M113" s="10">
-        <v>0.24744027303754265</v>
       </c>
     </row>
     <row r="114" spans="1:13" s="4" customFormat="1">
@@ -7389,11 +7390,11 @@
       <c r="K114" s="10">
         <v>0</v>
       </c>
-      <c r="L114" s="9" t="s">
+      <c r="L114" s="10">
+        <v>0.25831353919239908</v>
+      </c>
+      <c r="M114" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M114" s="10">
-        <v>0.25831353919239908</v>
       </c>
     </row>
     <row r="115" spans="1:13" s="4" customFormat="1">
@@ -7430,11 +7431,11 @@
       <c r="K115" s="10">
         <v>0</v>
       </c>
-      <c r="L115" s="9" t="s">
+      <c r="L115" s="10">
+        <v>0.29753761969904241</v>
+      </c>
+      <c r="M115" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M115" s="10">
-        <v>0.29753761969904241</v>
       </c>
     </row>
     <row r="116" spans="1:13" s="4" customFormat="1">
@@ -7471,11 +7472,11 @@
       <c r="K116" s="10">
         <v>0</v>
       </c>
-      <c r="L116" s="9" t="s">
+      <c r="L116" s="10">
+        <v>0.25831353919239908</v>
+      </c>
+      <c r="M116" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M116" s="10">
-        <v>0.25831353919239908</v>
       </c>
     </row>
     <row r="117" spans="1:13" s="4" customFormat="1">
@@ -7512,11 +7513,11 @@
       <c r="K117" s="10">
         <v>0</v>
       </c>
-      <c r="L117" s="9" t="s">
+      <c r="L117" s="10">
+        <v>0.25831353919239908</v>
+      </c>
+      <c r="M117" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M117" s="10">
-        <v>0.25831353919239908</v>
       </c>
     </row>
     <row r="118" spans="1:13">
@@ -7553,11 +7554,11 @@
       <c r="K118" s="10">
         <v>0.11395348837209303</v>
       </c>
-      <c r="L118" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M118" s="10">
-        <v>0</v>
+      <c r="L118" s="10">
+        <v>0</v>
+      </c>
+      <c r="M118" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="119" spans="1:13">
@@ -7594,11 +7595,11 @@
       <c r="K119" s="10">
         <v>9.4230769230769229E-2</v>
       </c>
-      <c r="L119" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M119" s="10">
-        <v>0</v>
+      <c r="L119" s="10">
+        <v>0</v>
+      </c>
+      <c r="M119" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="120" spans="1:13">
@@ -7635,11 +7636,11 @@
       <c r="K120" s="10">
         <v>9.4230769230769229E-2</v>
       </c>
-      <c r="L120" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M120" s="10">
-        <v>0</v>
+      <c r="L120" s="10">
+        <v>0</v>
+      </c>
+      <c r="M120" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="121" spans="1:13">
@@ -7676,11 +7677,11 @@
       <c r="K121" s="10">
         <v>0.14306569343065692</v>
       </c>
-      <c r="L121" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M121" s="10">
-        <v>0</v>
+      <c r="L121" s="10">
+        <v>0</v>
+      </c>
+      <c r="M121" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="122" spans="1:13">
@@ -7717,11 +7718,11 @@
       <c r="K122" s="10">
         <v>0.13333333333333336</v>
       </c>
-      <c r="L122" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M122" s="10">
-        <v>0</v>
+      <c r="L122" s="10">
+        <v>0</v>
+      </c>
+      <c r="M122" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="123" spans="1:13">
@@ -7758,11 +7759,11 @@
       <c r="K123" s="10">
         <v>0.10710382513661201</v>
       </c>
-      <c r="L123" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M123" s="10">
-        <v>0</v>
+      <c r="L123" s="10">
+        <v>0</v>
+      </c>
+      <c r="M123" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="124" spans="1:13">
@@ -7799,11 +7800,11 @@
       <c r="K124" s="10">
         <v>9.4230769230769229E-2</v>
       </c>
-      <c r="L124" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M124" s="10">
-        <v>0</v>
+      <c r="L124" s="10">
+        <v>0</v>
+      </c>
+      <c r="M124" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="125" spans="1:13">
@@ -7840,11 +7841,11 @@
       <c r="K125" s="10">
         <v>0.14306569343065692</v>
       </c>
-      <c r="L125" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M125" s="10">
-        <v>0</v>
+      <c r="L125" s="10">
+        <v>0</v>
+      </c>
+      <c r="M125" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="126" spans="1:13">
@@ -7881,11 +7882,11 @@
       <c r="K126" s="10">
         <v>0.13333333333333336</v>
       </c>
-      <c r="L126" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M126" s="10">
-        <v>0</v>
+      <c r="L126" s="10">
+        <v>0</v>
+      </c>
+      <c r="M126" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="127" spans="1:13">
@@ -7922,11 +7923,11 @@
       <c r="K127" s="10">
         <v>0.10710382513661201</v>
       </c>
-      <c r="L127" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M127" s="10">
-        <v>0</v>
+      <c r="L127" s="10">
+        <v>0</v>
+      </c>
+      <c r="M127" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="128" spans="1:13">
@@ -7963,11 +7964,11 @@
       <c r="K128" s="10">
         <v>9.4230769230769229E-2</v>
       </c>
-      <c r="L128" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M128" s="10">
-        <v>0</v>
+      <c r="L128" s="10">
+        <v>0</v>
+      </c>
+      <c r="M128" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="129" spans="1:13">
@@ -8004,11 +8005,11 @@
       <c r="K129" s="10">
         <v>0.1101123595505618</v>
       </c>
-      <c r="L129" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M129" s="10">
-        <v>0</v>
+      <c r="L129" s="10">
+        <v>0</v>
+      </c>
+      <c r="M129" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="130" spans="1:13">
@@ -8045,11 +8046,11 @@
       <c r="K130" s="10">
         <v>0.1101123595505618</v>
       </c>
-      <c r="L130" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M130" s="10">
-        <v>0</v>
+      <c r="L130" s="10">
+        <v>0</v>
+      </c>
+      <c r="M130" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="131" spans="1:13">
@@ -8086,11 +8087,11 @@
       <c r="K131" s="10">
         <v>9.4230769230769229E-2</v>
       </c>
-      <c r="L131" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M131" s="10">
-        <v>0</v>
+      <c r="L131" s="10">
+        <v>0</v>
+      </c>
+      <c r="M131" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="132" spans="1:13">
@@ -8127,11 +8128,11 @@
       <c r="K132" s="10">
         <v>0</v>
       </c>
-      <c r="L132" s="9" t="s">
+      <c r="L132" s="10">
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="M132" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M132" s="10">
-        <v>0.30769230769230771</v>
       </c>
     </row>
     <row r="133" spans="1:13">
@@ -8168,11 +8169,11 @@
       <c r="K133" s="10">
         <v>0</v>
       </c>
-      <c r="L133" s="9" t="s">
+      <c r="L133" s="10">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="M133" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M133" s="10">
-        <v>0.22222222222222221</v>
       </c>
     </row>
     <row r="134" spans="1:13">
@@ -8209,11 +8210,11 @@
       <c r="K134" s="10">
         <v>0</v>
       </c>
-      <c r="L134" s="9" t="s">
+      <c r="L134" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="M134" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M134" s="10">
-        <v>0.1</v>
       </c>
     </row>
     <row r="135" spans="1:13">
@@ -8250,11 +8251,11 @@
       <c r="K135" s="10">
         <v>0</v>
       </c>
-      <c r="L135" s="9" t="s">
+      <c r="L135" s="10">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="M135" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M135" s="10">
-        <v>0.22222222222222221</v>
       </c>
     </row>
     <row r="136" spans="1:13">
@@ -8291,11 +8292,11 @@
       <c r="K136" s="10">
         <v>0</v>
       </c>
-      <c r="L136" s="9" t="s">
+      <c r="L136" s="10">
+        <v>0.17391304347826086</v>
+      </c>
+      <c r="M136" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M136" s="10">
-        <v>0.17391304347826086</v>
       </c>
     </row>
     <row r="137" spans="1:13">
@@ -8332,11 +8333,11 @@
       <c r="K137" s="10">
         <v>0</v>
       </c>
-      <c r="L137" s="9" t="s">
+      <c r="L137" s="10">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="M137" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M137" s="10">
-        <v>0.14285714285714285</v>
       </c>
     </row>
     <row r="138" spans="1:13">
@@ -8373,11 +8374,11 @@
       <c r="K138" s="10">
         <v>0</v>
       </c>
-      <c r="L138" s="9" t="s">
+      <c r="L138" s="10">
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="M138" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M138" s="10">
-        <v>0.30769230769230771</v>
       </c>
     </row>
     <row r="139" spans="1:13">
@@ -8414,11 +8415,11 @@
       <c r="K139" s="10">
         <v>0</v>
       </c>
-      <c r="L139" s="9" t="s">
+      <c r="L139" s="10">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="M139" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M139" s="10">
-        <v>0.22222222222222221</v>
       </c>
     </row>
     <row r="140" spans="1:13">
@@ -8455,11 +8456,11 @@
       <c r="K140" s="10">
         <v>0</v>
       </c>
-      <c r="L140" s="9" t="s">
+      <c r="L140" s="10">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="M140" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M140" s="10">
-        <v>0.22222222222222221</v>
       </c>
     </row>
     <row r="141" spans="1:13">
@@ -8496,11 +8497,11 @@
       <c r="K141" s="10">
         <v>0</v>
       </c>
-      <c r="L141" s="9" t="s">
+      <c r="L141" s="10">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="M141" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M141" s="10">
-        <v>0.22222222222222221</v>
       </c>
     </row>
     <row r="142" spans="1:13">
@@ -8537,11 +8538,11 @@
       <c r="K142" s="10">
         <v>0</v>
       </c>
-      <c r="L142" s="9" t="s">
+      <c r="L142" s="10">
+        <v>0.17391304347826086</v>
+      </c>
+      <c r="M142" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M142" s="10">
-        <v>0.17391304347826086</v>
       </c>
     </row>
     <row r="143" spans="1:13">
@@ -8578,11 +8579,11 @@
       <c r="K143" s="10">
         <v>0</v>
       </c>
-      <c r="L143" s="9" t="s">
+      <c r="L143" s="10">
+        <v>0.17391304347826086</v>
+      </c>
+      <c r="M143" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M143" s="10">
-        <v>0.17391304347826086</v>
       </c>
     </row>
     <row r="144" spans="1:13">
@@ -8619,11 +8620,11 @@
       <c r="K144" s="10">
         <v>0</v>
       </c>
-      <c r="L144" s="9" t="s">
+      <c r="L144" s="10">
+        <v>0.17391304347826086</v>
+      </c>
+      <c r="M144" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M144" s="10">
-        <v>0.17391304347826086</v>
       </c>
     </row>
     <row r="145" spans="1:13">
@@ -8660,11 +8661,11 @@
       <c r="K145" s="10">
         <v>0</v>
       </c>
-      <c r="L145" s="9" t="s">
+      <c r="L145" s="10">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="M145" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M145" s="10">
-        <v>0.14285714285714285</v>
       </c>
     </row>
     <row r="146" spans="1:13">
@@ -8701,11 +8702,11 @@
       <c r="K146" s="10">
         <v>0</v>
       </c>
-      <c r="L146" s="9" t="s">
+      <c r="L146" s="10">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="M146" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M146" s="10">
-        <v>0.14285714285714285</v>
       </c>
     </row>
     <row r="147" spans="1:13">
@@ -8742,11 +8743,11 @@
       <c r="K147" s="10">
         <v>0</v>
       </c>
-      <c r="L147" s="9" t="s">
+      <c r="L147" s="10">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="M147" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M147" s="10">
-        <v>0.14285714285714285</v>
       </c>
     </row>
     <row r="148" spans="1:13">
@@ -8783,11 +8784,11 @@
       <c r="K148" s="10">
         <v>0</v>
       </c>
-      <c r="L148" s="9" t="s">
+      <c r="L148" s="10">
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="M148" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M148" s="10">
-        <v>0.30769230769230771</v>
       </c>
     </row>
     <row r="149" spans="1:13">
@@ -8824,11 +8825,11 @@
       <c r="K149" s="10">
         <v>0</v>
       </c>
-      <c r="L149" s="9" t="s">
+      <c r="L149" s="10">
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="M149" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M149" s="10">
-        <v>0.30769230769230771</v>
       </c>
     </row>
     <row r="150" spans="1:13">
@@ -8865,11 +8866,11 @@
       <c r="K150" s="10">
         <v>0</v>
       </c>
-      <c r="L150" s="9" t="s">
+      <c r="L150" s="10">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="M150" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M150" s="10">
-        <v>0.22222222222222221</v>
       </c>
     </row>
     <row r="151" spans="1:13">
@@ -8906,11 +8907,11 @@
       <c r="K151" s="10">
         <v>0</v>
       </c>
-      <c r="L151" s="9" t="s">
+      <c r="L151" s="10">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="M151" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M151" s="10">
-        <v>0.22222222222222221</v>
       </c>
     </row>
     <row r="152" spans="1:13">
@@ -8947,11 +8948,11 @@
       <c r="K152" s="10">
         <v>0</v>
       </c>
-      <c r="L152" s="9" t="s">
+      <c r="L152" s="10">
+        <v>0.17391304347826086</v>
+      </c>
+      <c r="M152" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M152" s="10">
-        <v>0.17391304347826086</v>
       </c>
     </row>
     <row r="153" spans="1:13">
@@ -8988,11 +8989,11 @@
       <c r="K153" s="10">
         <v>0</v>
       </c>
-      <c r="L153" s="9" t="s">
+      <c r="L153" s="10">
+        <v>0.17391304347826086</v>
+      </c>
+      <c r="M153" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M153" s="10">
-        <v>0.17391304347826086</v>
       </c>
     </row>
     <row r="154" spans="1:13">
@@ -9029,11 +9030,11 @@
       <c r="K154" s="10">
         <v>0</v>
       </c>
-      <c r="L154" s="9" t="s">
+      <c r="L154" s="10">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="M154" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M154" s="10">
-        <v>0.14285714285714285</v>
       </c>
     </row>
     <row r="155" spans="1:13">
@@ -9070,11 +9071,11 @@
       <c r="K155" s="10">
         <v>0</v>
       </c>
-      <c r="L155" s="9" t="s">
+      <c r="L155" s="10">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="M155" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M155" s="10">
-        <v>0.14285714285714285</v>
       </c>
     </row>
     <row r="156" spans="1:13">
@@ -9111,11 +9112,11 @@
       <c r="K156" s="10">
         <v>0</v>
       </c>
-      <c r="L156" s="9" t="s">
+      <c r="L156" s="10">
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="M156" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M156" s="10">
-        <v>0.30769230769230771</v>
       </c>
     </row>
     <row r="157" spans="1:13">
@@ -9152,11 +9153,11 @@
       <c r="K157" s="10">
         <v>0</v>
       </c>
-      <c r="L157" s="9" t="s">
+      <c r="L157" s="10">
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="M157" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M157" s="10">
-        <v>0.30769230769230771</v>
       </c>
     </row>
     <row r="158" spans="1:13">
@@ -9193,11 +9194,11 @@
       <c r="K158" s="10">
         <v>0</v>
       </c>
-      <c r="L158" s="9" t="s">
+      <c r="L158" s="10">
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="M158" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M158" s="10">
-        <v>0.30769230769230771</v>
       </c>
     </row>
     <row r="159" spans="1:13">
@@ -9234,11 +9235,11 @@
       <c r="K159" s="10">
         <v>0</v>
       </c>
-      <c r="L159" s="9" t="s">
+      <c r="L159" s="10">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="M159" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M159" s="10">
-        <v>0.22222222222222221</v>
       </c>
     </row>
     <row r="160" spans="1:13">
@@ -9275,11 +9276,11 @@
       <c r="K160" s="10">
         <v>0</v>
       </c>
-      <c r="L160" s="9" t="s">
+      <c r="L160" s="10">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="M160" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M160" s="10">
-        <v>0.22222222222222221</v>
       </c>
     </row>
     <row r="161" spans="1:13">
@@ -9316,11 +9317,11 @@
       <c r="K161" s="10">
         <v>0</v>
       </c>
-      <c r="L161" s="9" t="s">
+      <c r="L161" s="10">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="M161" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M161" s="10">
-        <v>0.22222222222222221</v>
       </c>
     </row>
     <row r="162" spans="1:13">
@@ -9357,11 +9358,11 @@
       <c r="K162" s="10">
         <v>0</v>
       </c>
-      <c r="L162" s="9" t="s">
+      <c r="L162" s="10">
+        <v>0.17391304347826086</v>
+      </c>
+      <c r="M162" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M162" s="10">
-        <v>0.17391304347826086</v>
       </c>
     </row>
     <row r="163" spans="1:13">
@@ -9398,11 +9399,11 @@
       <c r="K163" s="10">
         <v>0</v>
       </c>
-      <c r="L163" s="9" t="s">
+      <c r="L163" s="10">
+        <v>0.17391304347826086</v>
+      </c>
+      <c r="M163" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M163" s="10">
-        <v>0.17391304347826086</v>
       </c>
     </row>
     <row r="164" spans="1:13">
@@ -9439,11 +9440,11 @@
       <c r="K164" s="10">
         <v>0</v>
       </c>
-      <c r="L164" s="9" t="s">
+      <c r="L164" s="10">
+        <v>0.17391304347826086</v>
+      </c>
+      <c r="M164" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M164" s="10">
-        <v>0.17391304347826086</v>
       </c>
     </row>
     <row r="165" spans="1:13">
@@ -9480,11 +9481,11 @@
       <c r="K165" s="10">
         <v>0</v>
       </c>
-      <c r="L165" s="9" t="s">
+      <c r="L165" s="10">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="M165" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M165" s="10">
-        <v>0.14285714285714285</v>
       </c>
     </row>
     <row r="166" spans="1:13">
@@ -9521,11 +9522,11 @@
       <c r="K166" s="10">
         <v>0</v>
       </c>
-      <c r="L166" s="9" t="s">
+      <c r="L166" s="10">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="M166" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M166" s="10">
-        <v>0.14285714285714285</v>
       </c>
     </row>
     <row r="167" spans="1:13">
@@ -9562,11 +9563,11 @@
       <c r="K167" s="10">
         <v>0</v>
       </c>
-      <c r="L167" s="9" t="s">
+      <c r="L167" s="10">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="M167" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M167" s="10">
-        <v>0.14285714285714285</v>
       </c>
     </row>
     <row r="168" spans="1:13">
@@ -9603,11 +9604,11 @@
       <c r="K168" s="10">
         <v>0</v>
       </c>
-      <c r="L168" s="9" t="s">
+      <c r="L168" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="M168" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M168" s="10">
-        <v>0.2</v>
       </c>
     </row>
     <row r="169" spans="1:13">
@@ -9644,11 +9645,11 @@
       <c r="K169" s="10">
         <v>0</v>
       </c>
-      <c r="L169" s="9" t="s">
+      <c r="L169" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="M169" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M169" s="10">
-        <v>0.2</v>
       </c>
     </row>
     <row r="170" spans="1:13">
@@ -9685,11 +9686,11 @@
       <c r="K170" s="10">
         <v>0</v>
       </c>
-      <c r="L170" s="9" t="s">
+      <c r="L170" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="M170" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M170" s="10">
-        <v>0.2</v>
       </c>
     </row>
     <row r="171" spans="1:13">
@@ -9726,11 +9727,11 @@
       <c r="K171" s="10">
         <v>0</v>
       </c>
-      <c r="L171" s="9" t="s">
+      <c r="L171" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="M171" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M171" s="10">
-        <v>0.2</v>
       </c>
     </row>
     <row r="172" spans="1:13">
@@ -9767,11 +9768,11 @@
       <c r="K172" s="10">
         <v>0</v>
       </c>
-      <c r="L172" s="9" t="s">
+      <c r="L172" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="M172" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M172" s="10">
-        <v>0.2</v>
       </c>
     </row>
     <row r="173" spans="1:13">
@@ -9808,11 +9809,11 @@
       <c r="K173" s="10">
         <v>0</v>
       </c>
-      <c r="L173" s="9" t="s">
+      <c r="L173" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="M173" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M173" s="10">
-        <v>0.2</v>
       </c>
     </row>
     <row r="174" spans="1:13">
@@ -9849,11 +9850,11 @@
       <c r="K174" s="10">
         <v>0</v>
       </c>
-      <c r="L174" s="9" t="s">
+      <c r="L174" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="M174" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M174" s="10">
-        <v>0.2</v>
       </c>
     </row>
     <row r="175" spans="1:13">
@@ -9890,11 +9891,11 @@
       <c r="K175" s="10">
         <v>0</v>
       </c>
-      <c r="L175" s="9" t="s">
+      <c r="L175" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="M175" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M175" s="10">
-        <v>0.2</v>
       </c>
     </row>
     <row r="176" spans="1:13">
@@ -9931,11 +9932,11 @@
       <c r="K176" s="10">
         <v>5.103703703703704E-2</v>
       </c>
-      <c r="L176" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M176" s="10">
-        <v>0</v>
+      <c r="L176" s="10">
+        <v>0</v>
+      </c>
+      <c r="M176" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="177" spans="1:13">
@@ -9972,11 +9973,11 @@
       <c r="K177" s="10">
         <v>5.6872427983539094E-2</v>
       </c>
-      <c r="L177" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M177" s="10">
-        <v>0</v>
+      <c r="L177" s="10">
+        <v>0</v>
+      </c>
+      <c r="M177" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="178" spans="1:13">
@@ -10013,11 +10014,11 @@
       <c r="K178" s="10">
         <v>5.8333333333333334E-2</v>
       </c>
-      <c r="L178" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M178" s="10">
-        <v>0</v>
+      <c r="L178" s="10">
+        <v>0</v>
+      </c>
+      <c r="M178" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="179" spans="1:13">
@@ -10054,11 +10055,11 @@
       <c r="K179" s="10">
         <v>5.664221678891606E-2</v>
       </c>
-      <c r="L179" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M179" s="10">
-        <v>0</v>
+      <c r="L179" s="10">
+        <v>0</v>
+      </c>
+      <c r="M179" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="180" spans="1:13">
@@ -10095,11 +10096,11 @@
       <c r="K180" s="10">
         <v>0.12828546562228024</v>
       </c>
-      <c r="L180" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M180" s="10">
-        <v>0</v>
+      <c r="L180" s="10">
+        <v>0</v>
+      </c>
+      <c r="M180" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="181" spans="1:13">
@@ -10136,11 +10137,11 @@
       <c r="K181" s="10">
         <v>0.10789473684210525</v>
       </c>
-      <c r="L181" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M181" s="10">
-        <v>0</v>
+      <c r="L181" s="10">
+        <v>0</v>
+      </c>
+      <c r="M181" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="182" spans="1:13">
@@ -10177,11 +10178,11 @@
       <c r="K182" s="10">
         <v>9.3576958966355608E-2</v>
       </c>
-      <c r="L182" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M182" s="10">
-        <v>0</v>
+      <c r="L182" s="10">
+        <v>0</v>
+      </c>
+      <c r="M182" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="183" spans="1:13">
@@ -10218,11 +10219,11 @@
       <c r="K183" s="10">
         <v>9.4812298358650737E-2</v>
       </c>
-      <c r="L183" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M183" s="10">
-        <v>0</v>
+      <c r="L183" s="10">
+        <v>0</v>
+      </c>
+      <c r="M183" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="184" spans="1:13">
@@ -10259,11 +10260,11 @@
       <c r="K184" s="10">
         <v>8.4994456812636607E-2</v>
       </c>
-      <c r="L184" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M184" s="10">
-        <v>0</v>
+      <c r="L184" s="10">
+        <v>0</v>
+      </c>
+      <c r="M184" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="185" spans="1:13">
@@ -10300,11 +10301,11 @@
       <c r="K185" s="10">
         <v>9.1490848416150225E-2</v>
       </c>
-      <c r="L185" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M185" s="10">
-        <v>0</v>
+      <c r="L185" s="10">
+        <v>0</v>
+      </c>
+      <c r="M185" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="186" spans="1:13">
@@ -10341,11 +10342,11 @@
       <c r="K186" s="10">
         <v>9.2671375492487648E-2</v>
       </c>
-      <c r="L186" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M186" s="10">
-        <v>0</v>
+      <c r="L186" s="10">
+        <v>0</v>
+      </c>
+      <c r="M186" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="187" spans="1:13">
@@ -10382,11 +10383,11 @@
       <c r="K187" s="10">
         <v>9.0625004424830194E-2</v>
       </c>
-      <c r="L187" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M187" s="10">
-        <v>0</v>
+      <c r="L187" s="10">
+        <v>0</v>
+      </c>
+      <c r="M187" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="188" spans="1:13">
@@ -10423,11 +10424,11 @@
       <c r="K188" s="10">
         <v>0.19369565217391305</v>
       </c>
-      <c r="L188" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M188" s="10">
-        <v>0</v>
+      <c r="L188" s="10">
+        <v>0</v>
+      </c>
+      <c r="M188" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="189" spans="1:13">
@@ -10464,11 +10465,11 @@
       <c r="K189" s="10">
         <v>0.27860696517412931</v>
       </c>
-      <c r="L189" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M189" s="10">
-        <v>0</v>
+      <c r="L189" s="10">
+        <v>0</v>
+      </c>
+      <c r="M189" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="190" spans="1:13">
@@ -10505,11 +10506,11 @@
       <c r="K190" s="10">
         <v>0.19712296983758701</v>
       </c>
-      <c r="L190" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M190" s="10">
-        <v>0</v>
+      <c r="L190" s="10">
+        <v>0</v>
+      </c>
+      <c r="M190" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="191" spans="1:13">
@@ -10546,11 +10547,11 @@
       <c r="K191" s="10">
         <v>0.28342939481268009</v>
       </c>
-      <c r="L191" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M191" s="10">
-        <v>0</v>
+      <c r="L191" s="10">
+        <v>0</v>
+      </c>
+      <c r="M191" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="192" spans="1:13">
@@ -10587,11 +10588,11 @@
       <c r="K192" s="10">
         <v>0.15015641293013557</v>
       </c>
-      <c r="L192" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M192" s="10">
-        <v>0</v>
+      <c r="L192" s="10">
+        <v>0</v>
+      </c>
+      <c r="M192" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="193" spans="1:13">
@@ -10628,11 +10629,11 @@
       <c r="K193" s="10">
         <v>0.14963503649635038</v>
       </c>
-      <c r="L193" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M193" s="10">
-        <v>0</v>
+      <c r="L193" s="10">
+        <v>0</v>
+      </c>
+      <c r="M193" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="194" spans="1:13">
@@ -10669,11 +10670,11 @@
       <c r="K194" s="10">
         <v>0.14963503649635038</v>
       </c>
-      <c r="L194" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M194" s="10">
-        <v>0</v>
+      <c r="L194" s="10">
+        <v>0</v>
+      </c>
+      <c r="M194" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="195" spans="1:13">
@@ -10710,11 +10711,11 @@
       <c r="K195" s="10">
         <v>0.14963503649635038</v>
       </c>
-      <c r="L195" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M195" s="10">
-        <v>0</v>
+      <c r="L195" s="10">
+        <v>0</v>
+      </c>
+      <c r="M195" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="196" spans="1:13">
@@ -10751,11 +10752,11 @@
       <c r="K196" s="10">
         <v>0.14963503649635038</v>
       </c>
-      <c r="L196" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M196" s="10">
-        <v>0</v>
+      <c r="L196" s="10">
+        <v>0</v>
+      </c>
+      <c r="M196" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="197" spans="1:13">
@@ -10792,11 +10793,11 @@
       <c r="K197" s="10">
         <v>0.14963503649635038</v>
       </c>
-      <c r="L197" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M197" s="10">
-        <v>0</v>
+      <c r="L197" s="10">
+        <v>0</v>
+      </c>
+      <c r="M197" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="198" spans="1:13" s="4" customFormat="1">
@@ -10833,11 +10834,11 @@
       <c r="K198" s="10">
         <v>0</v>
       </c>
-      <c r="L198" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M198" s="10">
-        <v>0</v>
+      <c r="L198" s="10">
+        <v>0</v>
+      </c>
+      <c r="M198" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="199" spans="1:13" s="4" customFormat="1">
@@ -10874,11 +10875,11 @@
       <c r="K199" s="10">
         <v>0</v>
       </c>
-      <c r="L199" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M199" s="10">
-        <v>0</v>
+      <c r="L199" s="10">
+        <v>0</v>
+      </c>
+      <c r="M199" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="200" spans="1:13" s="4" customFormat="1">
@@ -10915,11 +10916,11 @@
       <c r="K200" s="10">
         <v>0</v>
       </c>
-      <c r="L200" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M200" s="10">
-        <v>0</v>
+      <c r="L200" s="10">
+        <v>0</v>
+      </c>
+      <c r="M200" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="201" spans="1:13" s="4" customFormat="1">
@@ -10956,11 +10957,11 @@
       <c r="K201" s="10">
         <v>0</v>
       </c>
-      <c r="L201" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M201" s="10">
-        <v>0</v>
+      <c r="L201" s="10">
+        <v>0</v>
+      </c>
+      <c r="M201" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="202" spans="1:13" s="4" customFormat="1">
@@ -10997,11 +10998,11 @@
       <c r="K202" s="10">
         <v>0</v>
       </c>
-      <c r="L202" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M202" s="10">
-        <v>0</v>
+      <c r="L202" s="10">
+        <v>0</v>
+      </c>
+      <c r="M202" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="203" spans="1:13" s="4" customFormat="1">
@@ -11038,11 +11039,11 @@
       <c r="K203" s="10">
         <v>0</v>
       </c>
-      <c r="L203" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M203" s="10">
-        <v>0</v>
+      <c r="L203" s="10">
+        <v>0</v>
+      </c>
+      <c r="M203" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="204" spans="1:13" s="4" customFormat="1">
@@ -11079,11 +11080,11 @@
       <c r="K204" s="10">
         <v>0</v>
       </c>
-      <c r="L204" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M204" s="10">
-        <v>0</v>
+      <c r="L204" s="10">
+        <v>0</v>
+      </c>
+      <c r="M204" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="205" spans="1:13" s="4" customFormat="1">
@@ -11120,11 +11121,11 @@
       <c r="K205" s="10">
         <v>0</v>
       </c>
-      <c r="L205" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M205" s="10">
-        <v>0</v>
+      <c r="L205" s="10">
+        <v>0</v>
+      </c>
+      <c r="M205" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="206" spans="1:13" s="4" customFormat="1">
@@ -11161,11 +11162,11 @@
       <c r="K206" s="10">
         <v>0</v>
       </c>
-      <c r="L206" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M206" s="10">
-        <v>0</v>
+      <c r="L206" s="10">
+        <v>0</v>
+      </c>
+      <c r="M206" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="207" spans="1:13" s="4" customFormat="1">
@@ -11202,11 +11203,11 @@
       <c r="K207" s="10">
         <v>0</v>
       </c>
-      <c r="L207" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M207" s="10">
-        <v>0</v>
+      <c r="L207" s="10">
+        <v>0</v>
+      </c>
+      <c r="M207" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="208" spans="1:13" s="4" customFormat="1">
@@ -11243,11 +11244,11 @@
       <c r="K208" s="10">
         <v>0</v>
       </c>
-      <c r="L208" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M208" s="10">
-        <v>0</v>
+      <c r="L208" s="10">
+        <v>0</v>
+      </c>
+      <c r="M208" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="209" spans="1:13" s="4" customFormat="1">
@@ -11284,11 +11285,11 @@
       <c r="K209" s="10">
         <v>0</v>
       </c>
-      <c r="L209" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M209" s="10">
-        <v>0</v>
+      <c r="L209" s="10">
+        <v>0</v>
+      </c>
+      <c r="M209" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="210" spans="1:13" s="4" customFormat="1">
@@ -11325,11 +11326,11 @@
       <c r="K210" s="10">
         <v>0</v>
       </c>
-      <c r="L210" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M210" s="10">
-        <v>0</v>
+      <c r="L210" s="10">
+        <v>0</v>
+      </c>
+      <c r="M210" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="211" spans="1:13" s="4" customFormat="1">
@@ -11366,11 +11367,11 @@
       <c r="K211" s="10">
         <v>0</v>
       </c>
-      <c r="L211" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M211" s="10">
-        <v>0</v>
+      <c r="L211" s="10">
+        <v>0</v>
+      </c>
+      <c r="M211" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="212" spans="1:13" s="4" customFormat="1">
@@ -11407,11 +11408,11 @@
       <c r="K212" s="10">
         <v>0</v>
       </c>
-      <c r="L212" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M212" s="10">
-        <v>0</v>
+      <c r="L212" s="10">
+        <v>0</v>
+      </c>
+      <c r="M212" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="213" spans="1:13" s="4" customFormat="1">
@@ -11448,11 +11449,11 @@
       <c r="K213" s="10">
         <v>0</v>
       </c>
-      <c r="L213" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M213" s="10">
-        <v>0</v>
+      <c r="L213" s="10">
+        <v>0</v>
+      </c>
+      <c r="M213" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="214" spans="1:13" s="4" customFormat="1">
@@ -11489,11 +11490,11 @@
       <c r="K214" s="10">
         <v>0</v>
       </c>
-      <c r="L214" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M214" s="10">
-        <v>0</v>
+      <c r="L214" s="10">
+        <v>0</v>
+      </c>
+      <c r="M214" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="215" spans="1:13" s="4" customFormat="1">
@@ -11530,11 +11531,11 @@
       <c r="K215" s="10">
         <v>0</v>
       </c>
-      <c r="L215" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M215" s="10">
-        <v>0</v>
+      <c r="L215" s="10">
+        <v>0</v>
+      </c>
+      <c r="M215" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="216" spans="1:13" s="4" customFormat="1">
@@ -11571,11 +11572,11 @@
       <c r="K216" s="10">
         <v>0</v>
       </c>
-      <c r="L216" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M216" s="10">
-        <v>0</v>
+      <c r="L216" s="10">
+        <v>0</v>
+      </c>
+      <c r="M216" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="217" spans="1:13" s="4" customFormat="1">
@@ -11612,11 +11613,11 @@
       <c r="K217" s="10">
         <v>0</v>
       </c>
-      <c r="L217" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M217" s="10">
-        <v>0</v>
+      <c r="L217" s="10">
+        <v>0</v>
+      </c>
+      <c r="M217" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="218" spans="1:13" s="4" customFormat="1">
@@ -11653,11 +11654,11 @@
       <c r="K218" s="10">
         <v>0</v>
       </c>
-      <c r="L218" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M218" s="10">
-        <v>0</v>
+      <c r="L218" s="10">
+        <v>0</v>
+      </c>
+      <c r="M218" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="219" spans="1:13" s="4" customFormat="1">
@@ -11694,11 +11695,11 @@
       <c r="K219" s="10">
         <v>0</v>
       </c>
-      <c r="L219" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M219" s="10">
-        <v>0</v>
+      <c r="L219" s="10">
+        <v>0</v>
+      </c>
+      <c r="M219" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="220" spans="1:13" s="4" customFormat="1">
@@ -11735,11 +11736,11 @@
       <c r="K220" s="10">
         <v>0</v>
       </c>
-      <c r="L220" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M220" s="10">
-        <v>0</v>
+      <c r="L220" s="10">
+        <v>0</v>
+      </c>
+      <c r="M220" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="221" spans="1:13" s="4" customFormat="1">
@@ -11776,11 +11777,11 @@
       <c r="K221" s="10">
         <v>0</v>
       </c>
-      <c r="L221" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M221" s="10">
-        <v>0</v>
+      <c r="L221" s="10">
+        <v>0</v>
+      </c>
+      <c r="M221" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="222" spans="1:13" s="4" customFormat="1">
@@ -11817,11 +11818,11 @@
       <c r="K222" s="10">
         <v>0</v>
       </c>
-      <c r="L222" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M222" s="10">
-        <v>0</v>
+      <c r="L222" s="10">
+        <v>0</v>
+      </c>
+      <c r="M222" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="223" spans="1:13" s="4" customFormat="1">
@@ -11858,11 +11859,11 @@
       <c r="K223" s="10">
         <v>0</v>
       </c>
-      <c r="L223" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M223" s="10">
-        <v>0</v>
+      <c r="L223" s="10">
+        <v>0</v>
+      </c>
+      <c r="M223" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="224" spans="1:13">
@@ -11899,11 +11900,11 @@
       <c r="K224" s="10">
         <v>9.9999999999999992E-2</v>
       </c>
-      <c r="L224" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M224" s="10">
-        <v>0</v>
+      <c r="L224" s="10">
+        <v>0</v>
+      </c>
+      <c r="M224" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="225" spans="1:13">
@@ -11940,11 +11941,11 @@
       <c r="K225" s="10">
         <v>0.1</v>
       </c>
-      <c r="L225" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M225" s="10">
-        <v>0</v>
+      <c r="L225" s="10">
+        <v>0</v>
+      </c>
+      <c r="M225" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="226" spans="1:13">
@@ -11981,11 +11982,11 @@
       <c r="K226" s="10">
         <v>0</v>
       </c>
-      <c r="L226" s="9" t="s">
+      <c r="L226" s="10">
+        <v>0.20876112251882273</v>
+      </c>
+      <c r="M226" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M226" s="10">
-        <v>0.20876112251882273</v>
       </c>
     </row>
     <row r="227" spans="1:13">
@@ -12022,11 +12023,11 @@
       <c r="K227" s="10">
         <v>0</v>
       </c>
-      <c r="L227" s="9" t="s">
+      <c r="L227" s="10">
+        <v>0.20876112251882273</v>
+      </c>
+      <c r="M227" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M227" s="10">
-        <v>0.20876112251882273</v>
       </c>
     </row>
     <row r="228" spans="1:13">
@@ -12063,11 +12064,11 @@
       <c r="K228" s="10">
         <v>0</v>
       </c>
-      <c r="L228" s="9" t="s">
+      <c r="L228" s="10">
+        <v>0.20876112251882273</v>
+      </c>
+      <c r="M228" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M228" s="10">
-        <v>0.20876112251882273</v>
       </c>
     </row>
     <row r="229" spans="1:13">
@@ -12104,11 +12105,11 @@
       <c r="K229" s="10">
         <v>0</v>
       </c>
-      <c r="L229" s="9" t="s">
+      <c r="L229" s="10">
+        <v>0.20876112251882273</v>
+      </c>
+      <c r="M229" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M229" s="10">
-        <v>0.20876112251882273</v>
       </c>
     </row>
     <row r="230" spans="1:13">
@@ -12145,11 +12146,11 @@
       <c r="K230" s="10">
         <v>0</v>
       </c>
-      <c r="L230" s="9" t="s">
+      <c r="L230" s="10">
+        <v>0.20876112251882273</v>
+      </c>
+      <c r="M230" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M230" s="10">
-        <v>0.20876112251882273</v>
       </c>
     </row>
     <row r="231" spans="1:13">
@@ -12186,11 +12187,11 @@
       <c r="K231" s="10">
         <v>0</v>
       </c>
-      <c r="L231" s="9" t="s">
+      <c r="L231" s="10">
+        <v>0.20876112251882273</v>
+      </c>
+      <c r="M231" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M231" s="10">
-        <v>0.20876112251882273</v>
       </c>
     </row>
     <row r="232" spans="1:13">
@@ -12227,11 +12228,11 @@
       <c r="K232" s="10">
         <v>0</v>
       </c>
-      <c r="L232" s="9" t="s">
+      <c r="L232" s="10">
+        <v>0.20876112251882273</v>
+      </c>
+      <c r="M232" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M232" s="10">
-        <v>0.20876112251882273</v>
       </c>
     </row>
     <row r="233" spans="1:13">
@@ -12268,11 +12269,11 @@
       <c r="K233" s="10">
         <v>0</v>
       </c>
-      <c r="L233" s="9" t="s">
+      <c r="L233" s="10">
+        <v>0.20876112251882273</v>
+      </c>
+      <c r="M233" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M233" s="10">
-        <v>0.20876112251882273</v>
       </c>
     </row>
     <row r="234" spans="1:13">
@@ -12309,11 +12310,11 @@
       <c r="K234" s="10">
         <v>9.7851728895718276E-2</v>
       </c>
-      <c r="L234" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M234" s="10">
-        <v>0</v>
+      <c r="L234" s="10">
+        <v>0</v>
+      </c>
+      <c r="M234" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="235" spans="1:13">
@@ -12350,11 +12351,11 @@
       <c r="K235" s="10">
         <v>0.19570345779143655</v>
       </c>
-      <c r="L235" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M235" s="10">
-        <v>0</v>
+      <c r="L235" s="10">
+        <v>0</v>
+      </c>
+      <c r="M235" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="236" spans="1:13" s="4" customFormat="1">
@@ -12391,11 +12392,11 @@
       <c r="K236" s="10">
         <v>0.19700551615445233</v>
       </c>
-      <c r="L236" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M236" s="10">
-        <v>0</v>
+      <c r="L236" s="10">
+        <v>0</v>
+      </c>
+      <c r="M236" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="237" spans="1:13" s="4" customFormat="1">
@@ -12432,11 +12433,11 @@
       <c r="K237" s="10">
         <v>0</v>
       </c>
-      <c r="L237" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M237" s="10">
-        <v>0</v>
+      <c r="L237" s="10">
+        <v>0</v>
+      </c>
+      <c r="M237" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="238" spans="1:13">
@@ -12473,11 +12474,11 @@
       <c r="K238" s="10">
         <v>0.10814668423364074</v>
       </c>
-      <c r="L238" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M238" s="10">
-        <v>0</v>
+      <c r="L238" s="10">
+        <v>0</v>
+      </c>
+      <c r="M238" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="239" spans="1:13">
@@ -12514,11 +12515,11 @@
       <c r="K239" s="10">
         <v>0.21629336846728148</v>
       </c>
-      <c r="L239" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M239" s="10">
-        <v>0</v>
+      <c r="L239" s="10">
+        <v>0</v>
+      </c>
+      <c r="M239" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="240" spans="1:13">
@@ -12555,11 +12556,11 @@
       <c r="K240" s="10">
         <v>0.32444005270092224</v>
       </c>
-      <c r="L240" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M240" s="10">
-        <v>0</v>
+      <c r="L240" s="10">
+        <v>0</v>
+      </c>
+      <c r="M240" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="241" spans="1:13">
@@ -12596,11 +12597,11 @@
       <c r="K241" s="10">
         <v>0.43258673693456295</v>
       </c>
-      <c r="L241" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M241" s="10">
-        <v>0</v>
+      <c r="L241" s="10">
+        <v>0</v>
+      </c>
+      <c r="M241" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="242" spans="1:13">
@@ -12637,11 +12638,11 @@
       <c r="K242" s="10">
         <v>0.41728158205430932</v>
       </c>
-      <c r="L242" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M242" s="10">
-        <v>0</v>
+      <c r="L242" s="10">
+        <v>0</v>
+      </c>
+      <c r="M242" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="243" spans="1:13">
@@ -12678,11 +12679,11 @@
       <c r="K243" s="10">
         <v>0.41728158205430932</v>
       </c>
-      <c r="L243" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M243" s="10">
-        <v>0</v>
+      <c r="L243" s="10">
+        <v>0</v>
+      </c>
+      <c r="M243" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="244" spans="1:13">
@@ -12719,11 +12720,11 @@
       <c r="K244" s="10">
         <v>0.41728158205430932</v>
       </c>
-      <c r="L244" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M244" s="10">
-        <v>0</v>
+      <c r="L244" s="10">
+        <v>0</v>
+      </c>
+      <c r="M244" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="245" spans="1:13">
@@ -12760,11 +12761,11 @@
       <c r="K245" s="10">
         <v>0.21629336846728148</v>
       </c>
-      <c r="L245" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M245" s="10">
-        <v>0</v>
+      <c r="L245" s="10">
+        <v>0</v>
+      </c>
+      <c r="M245" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="246" spans="1:13">
@@ -12801,11 +12802,11 @@
       <c r="K246" s="10">
         <v>0.41728158205430932</v>
       </c>
-      <c r="L246" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M246" s="10">
-        <v>0</v>
+      <c r="L246" s="10">
+        <v>0</v>
+      </c>
+      <c r="M246" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="247" spans="1:13">
@@ -12842,11 +12843,11 @@
       <c r="K247" s="10">
         <v>0.41728158205430932</v>
       </c>
-      <c r="L247" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M247" s="10">
-        <v>0</v>
+      <c r="L247" s="10">
+        <v>0</v>
+      </c>
+      <c r="M247" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="248" spans="1:13">
@@ -12883,11 +12884,11 @@
       <c r="K248" s="10">
         <v>0.41728158205430932</v>
       </c>
-      <c r="L248" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M248" s="10">
-        <v>0</v>
+      <c r="L248" s="10">
+        <v>0</v>
+      </c>
+      <c r="M248" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="249" spans="1:13">
@@ -12924,11 +12925,11 @@
       <c r="K249" s="10">
         <v>0.41728158205430932</v>
       </c>
-      <c r="L249" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M249" s="10">
-        <v>0</v>
+      <c r="L249" s="10">
+        <v>0</v>
+      </c>
+      <c r="M249" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="250" spans="1:13">
@@ -12965,11 +12966,11 @@
       <c r="K250" s="10">
         <v>0.41728158205430932</v>
       </c>
-      <c r="L250" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M250" s="10">
-        <v>0</v>
+      <c r="L250" s="10">
+        <v>0</v>
+      </c>
+      <c r="M250" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="251" spans="1:13">
@@ -13006,11 +13007,11 @@
       <c r="K251" s="10">
         <v>0.41728158205430932</v>
       </c>
-      <c r="L251" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M251" s="10">
-        <v>0</v>
+      <c r="L251" s="10">
+        <v>0</v>
+      </c>
+      <c r="M251" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="252" spans="1:13">
@@ -13047,11 +13048,11 @@
       <c r="K252" s="10">
         <v>0.41728158205430932</v>
       </c>
-      <c r="L252" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M252" s="10">
-        <v>0</v>
+      <c r="L252" s="10">
+        <v>0</v>
+      </c>
+      <c r="M252" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="253" spans="1:13">
@@ -13088,11 +13089,11 @@
       <c r="K253" s="10">
         <v>0.41728158205430932</v>
       </c>
-      <c r="L253" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M253" s="10">
-        <v>0</v>
+      <c r="L253" s="10">
+        <v>0</v>
+      </c>
+      <c r="M253" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="254" spans="1:13">
@@ -13129,11 +13130,11 @@
       <c r="K254" s="10">
         <v>0.41728158205430932</v>
       </c>
-      <c r="L254" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M254" s="10">
-        <v>0</v>
+      <c r="L254" s="10">
+        <v>0</v>
+      </c>
+      <c r="M254" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="255" spans="1:13">
@@ -13170,11 +13171,11 @@
       <c r="K255" s="10">
         <v>0.41728158205430932</v>
       </c>
-      <c r="L255" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M255" s="10">
-        <v>0</v>
+      <c r="L255" s="10">
+        <v>0</v>
+      </c>
+      <c r="M255" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="256" spans="1:13">
@@ -13211,11 +13212,11 @@
       <c r="K256" s="10">
         <v>2.6627218934911243E-2</v>
       </c>
-      <c r="L256" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M256" s="10">
-        <v>0</v>
+      <c r="L256" s="10">
+        <v>0</v>
+      </c>
+      <c r="M256" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="257" spans="1:13">
@@ -13252,11 +13253,11 @@
       <c r="K257" s="10">
         <v>2.7450980392156862E-2</v>
       </c>
-      <c r="L257" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M257" s="10">
-        <v>0</v>
+      <c r="L257" s="10">
+        <v>0</v>
+      </c>
+      <c r="M257" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="258" spans="1:13">
@@ -13293,11 +13294,11 @@
       <c r="K258" s="10">
         <v>9.673852957435046E-2</v>
       </c>
-      <c r="L258" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M258" s="10">
-        <v>0</v>
+      <c r="L258" s="10">
+        <v>0</v>
+      </c>
+      <c r="M258" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="259" spans="1:13">
@@ -13334,11 +13335,11 @@
       <c r="K259" s="10">
         <v>4.9521857923497267E-2</v>
       </c>
-      <c r="L259" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M259" s="10">
-        <v>0</v>
+      <c r="L259" s="10">
+        <v>0</v>
+      </c>
+      <c r="M259" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="260" spans="1:13">
@@ -13375,11 +13376,11 @@
       <c r="K260" s="10">
         <v>0</v>
       </c>
-      <c r="L260" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M260" s="10">
-        <v>0</v>
+      <c r="L260" s="10">
+        <v>0</v>
+      </c>
+      <c r="M260" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="261" spans="1:13" s="4" customFormat="1">
@@ -13416,11 +13417,11 @@
       <c r="K261" s="10">
         <v>0</v>
       </c>
-      <c r="L261" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M261" s="10">
-        <v>0</v>
+      <c r="L261" s="10">
+        <v>0</v>
+      </c>
+      <c r="M261" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="262" spans="1:13" s="4" customFormat="1">
@@ -13457,11 +13458,11 @@
       <c r="K262" s="10">
         <v>0</v>
       </c>
-      <c r="L262" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M262" s="10">
-        <v>0</v>
+      <c r="L262" s="10">
+        <v>0</v>
+      </c>
+      <c r="M262" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="263" spans="1:13" s="4" customFormat="1">
@@ -13498,11 +13499,11 @@
       <c r="K263" s="10">
         <v>0</v>
       </c>
-      <c r="L263" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M263" s="10">
-        <v>0</v>
+      <c r="L263" s="10">
+        <v>0</v>
+      </c>
+      <c r="M263" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="264" spans="1:13">
@@ -13539,11 +13540,11 @@
       <c r="K264" s="10">
         <v>3.1080031080031083E-2</v>
       </c>
-      <c r="L264" s="9" t="s">
+      <c r="L264" s="10">
+        <v>0.15384615384615385</v>
+      </c>
+      <c r="M264" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M264" s="10">
-        <v>0.15384615384615385</v>
       </c>
     </row>
     <row r="265" spans="1:13">
@@ -13580,11 +13581,11 @@
       <c r="K265" s="10">
         <v>0</v>
       </c>
-      <c r="L265" s="9" t="s">
+      <c r="L265" s="10">
+        <v>0.17123287671232876</v>
+      </c>
+      <c r="M265" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M265" s="10">
-        <v>0.17123287671232876</v>
       </c>
     </row>
     <row r="266" spans="1:13">
@@ -13621,11 +13622,11 @@
       <c r="K266" s="10">
         <v>0</v>
       </c>
-      <c r="L266" s="9" t="s">
+      <c r="L266" s="10">
+        <v>0.17123287671232876</v>
+      </c>
+      <c r="M266" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M266" s="10">
-        <v>0.17123287671232876</v>
       </c>
     </row>
     <row r="267" spans="1:13">
@@ -13662,11 +13663,11 @@
       <c r="K267" s="10">
         <v>0</v>
       </c>
-      <c r="L267" s="9" t="s">
+      <c r="L267" s="10">
+        <v>0.13919821826280623</v>
+      </c>
+      <c r="M267" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M267" s="10">
-        <v>0.13919821826280623</v>
       </c>
     </row>
     <row r="268" spans="1:13">
@@ -13703,11 +13704,11 @@
       <c r="K268" s="10">
         <v>0</v>
       </c>
-      <c r="L268" s="9" t="s">
+      <c r="L268" s="10">
+        <v>0.13919821826280623</v>
+      </c>
+      <c r="M268" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M268" s="10">
-        <v>0.13919821826280623</v>
       </c>
     </row>
     <row r="269" spans="1:13">
@@ -13744,11 +13745,11 @@
       <c r="K269" s="10">
         <v>9.9999999999999992E-2</v>
       </c>
-      <c r="L269" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M269" s="10">
-        <v>0</v>
+      <c r="L269" s="10">
+        <v>0</v>
+      </c>
+      <c r="M269" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="270" spans="1:13">
@@ -13785,11 +13786,11 @@
       <c r="K270" s="10">
         <v>0.16343805958000979</v>
       </c>
-      <c r="L270" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M270" s="10">
-        <v>0</v>
+      <c r="L270" s="10">
+        <v>0</v>
+      </c>
+      <c r="M270" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="271" spans="1:13">
@@ -13826,11 +13827,11 @@
       <c r="K271" s="10">
         <v>0.13648722131593258</v>
       </c>
-      <c r="L271" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M271" s="10">
-        <v>0</v>
+      <c r="L271" s="10">
+        <v>0</v>
+      </c>
+      <c r="M271" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="272" spans="1:13">
@@ -13867,11 +13868,11 @@
       <c r="K272" s="10">
         <v>0.13329792883696231</v>
       </c>
-      <c r="L272" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M272" s="10">
-        <v>0</v>
+      <c r="L272" s="10">
+        <v>0</v>
+      </c>
+      <c r="M272" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="273" spans="1:13">
@@ -13908,11 +13909,11 @@
       <c r="K273" s="10">
         <v>0.11671704254824461</v>
       </c>
-      <c r="L273" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M273" s="10">
-        <v>0</v>
+      <c r="L273" s="10">
+        <v>0</v>
+      </c>
+      <c r="M273" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="274" spans="1:13" s="4" customFormat="1">
@@ -13949,11 +13950,11 @@
       <c r="K274" s="10">
         <v>0</v>
       </c>
-      <c r="L274" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M274" s="10">
-        <v>0</v>
+      <c r="L274" s="10">
+        <v>0</v>
+      </c>
+      <c r="M274" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="275" spans="1:13">
@@ -13990,11 +13991,11 @@
       <c r="K275" s="10">
         <v>0</v>
       </c>
-      <c r="L275" s="9" t="s">
+      <c r="L275" s="10">
+        <v>0.4432624113475177</v>
+      </c>
+      <c r="M275" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M275" s="10">
-        <v>0.4432624113475177</v>
       </c>
     </row>
     <row r="276" spans="1:13">
@@ -14031,11 +14032,11 @@
       <c r="K276" s="10">
         <v>0</v>
       </c>
-      <c r="L276" s="9" t="s">
+      <c r="L276" s="10">
+        <v>0.41946308724832215</v>
+      </c>
+      <c r="M276" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M276" s="10">
-        <v>0.41946308724832215</v>
       </c>
     </row>
     <row r="277" spans="1:13">
@@ -14072,11 +14073,11 @@
       <c r="K277" s="10">
         <v>0</v>
       </c>
-      <c r="L277" s="9" t="s">
+      <c r="L277" s="10">
+        <v>0.25</v>
+      </c>
+      <c r="M277" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M277" s="10">
-        <v>0.25</v>
       </c>
     </row>
     <row r="278" spans="1:13">
@@ -14113,11 +14114,11 @@
       <c r="K278" s="10">
         <v>0</v>
       </c>
-      <c r="L278" s="9" t="s">
+      <c r="L278" s="10">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="M278" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M278" s="10">
-        <v>0.22222222222222221</v>
       </c>
     </row>
     <row r="279" spans="1:13">
@@ -14154,11 +14155,11 @@
       <c r="K279" s="10">
         <v>0.10944014294222752</v>
       </c>
-      <c r="L279" s="9" t="s">
+      <c r="L279" s="10">
+        <v>0.21739130434782608</v>
+      </c>
+      <c r="M279" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M279" s="10">
-        <v>0.21739130434782608</v>
       </c>
     </row>
     <row r="280" spans="1:13">
@@ -14195,11 +14196,11 @@
       <c r="K280" s="10">
         <v>0.1024247491638796</v>
       </c>
-      <c r="L280" s="9" t="s">
+      <c r="L280" s="10">
+        <v>0.21739130434782608</v>
+      </c>
+      <c r="M280" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M280" s="10">
-        <v>0.21739130434782608</v>
       </c>
     </row>
     <row r="281" spans="1:13">
@@ -14236,11 +14237,11 @@
       <c r="K281" s="10">
         <v>0.13435174304739522</v>
       </c>
-      <c r="L281" s="9" t="s">
+      <c r="L281" s="10">
+        <v>0.21739130434782608</v>
+      </c>
+      <c r="M281" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M281" s="10">
-        <v>0.21739130434782608</v>
       </c>
     </row>
     <row r="282" spans="1:13">
@@ -14277,11 +14278,11 @@
       <c r="K282" s="10">
         <v>0.15607580824972131</v>
       </c>
-      <c r="L282" s="9" t="s">
+      <c r="L282" s="10">
+        <v>0.21739130434782608</v>
+      </c>
+      <c r="M282" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M282" s="10">
-        <v>0.21739130434782608</v>
       </c>
     </row>
     <row r="283" spans="1:13">
@@ -14318,11 +14319,11 @@
       <c r="K283" s="10">
         <v>0.12365707693416973</v>
       </c>
-      <c r="L283" s="9" t="s">
+      <c r="L283" s="10">
+        <v>0.21739130434782608</v>
+      </c>
+      <c r="M283" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M283" s="10">
-        <v>0.21739130434782608</v>
       </c>
     </row>
     <row r="284" spans="1:13">
@@ -14359,11 +14360,11 @@
       <c r="K284" s="10">
         <v>0.13070152040544145</v>
       </c>
-      <c r="L284" s="9" t="s">
+      <c r="L284" s="10">
+        <v>0.21739130434782608</v>
+      </c>
+      <c r="M284" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M284" s="10">
-        <v>0.21739130434782608</v>
       </c>
     </row>
     <row r="285" spans="1:13">
@@ -14400,11 +14401,11 @@
       <c r="K285" s="10">
         <v>0.15152815934065933</v>
       </c>
-      <c r="L285" s="9" t="s">
+      <c r="L285" s="10">
+        <v>0.25</v>
+      </c>
+      <c r="M285" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M285" s="10">
-        <v>0.25</v>
       </c>
     </row>
     <row r="286" spans="1:13">
@@ -14441,11 +14442,11 @@
       <c r="K286" s="10">
         <v>0.10087025316455696</v>
       </c>
-      <c r="L286" s="9" t="s">
+      <c r="L286" s="10">
+        <v>0.25</v>
+      </c>
+      <c r="M286" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M286" s="10">
-        <v>0.25</v>
       </c>
     </row>
     <row r="287" spans="1:13">
@@ -14482,11 +14483,11 @@
       <c r="K287" s="10">
         <v>6.1791561712846339E-2</v>
       </c>
-      <c r="L287" s="9" t="s">
+      <c r="L287" s="10">
+        <v>0.25</v>
+      </c>
+      <c r="M287" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M287" s="10">
-        <v>0.25</v>
       </c>
     </row>
     <row r="288" spans="1:13">
@@ -14523,11 +14524,11 @@
       <c r="K288" s="10">
         <v>0.25594547563805103</v>
       </c>
-      <c r="L288" s="9" t="s">
+      <c r="L288" s="10">
+        <v>0.25</v>
+      </c>
+      <c r="M288" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M288" s="10">
-        <v>0.25</v>
       </c>
     </row>
     <row r="289" spans="1:13">
@@ -14564,11 +14565,11 @@
       <c r="K289" s="10">
         <v>0.25955882352941173</v>
       </c>
-      <c r="L289" s="9" t="s">
+      <c r="L289" s="10">
+        <v>0.25</v>
+      </c>
+      <c r="M289" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M289" s="10">
-        <v>0.25</v>
       </c>
     </row>
     <row r="290" spans="1:13">
@@ -14605,11 +14606,11 @@
       <c r="K290" s="10">
         <v>0</v>
       </c>
-      <c r="L290" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M290" s="10">
-        <v>0</v>
+      <c r="L290" s="10">
+        <v>0</v>
+      </c>
+      <c r="M290" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="291" spans="1:13">
@@ -14646,11 +14647,11 @@
       <c r="K291" s="10">
         <v>0</v>
       </c>
-      <c r="L291" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M291" s="10">
-        <v>0</v>
+      <c r="L291" s="10">
+        <v>0</v>
+      </c>
+      <c r="M291" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="292" spans="1:13">
@@ -14687,11 +14688,11 @@
       <c r="K292" s="10">
         <v>0</v>
       </c>
-      <c r="L292" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M292" s="10">
-        <v>0</v>
+      <c r="L292" s="10">
+        <v>0</v>
+      </c>
+      <c r="M292" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="293" spans="1:13">
@@ -14728,11 +14729,11 @@
       <c r="K293" s="10">
         <v>0</v>
       </c>
-      <c r="L293" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M293" s="10">
-        <v>0</v>
+      <c r="L293" s="10">
+        <v>0</v>
+      </c>
+      <c r="M293" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="294" spans="1:13">
@@ -14769,11 +14770,11 @@
       <c r="K294" s="10">
         <v>1.013327754273405E-4</v>
       </c>
-      <c r="L294" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M294" s="10">
-        <v>0</v>
+      <c r="L294" s="10">
+        <v>0</v>
+      </c>
+      <c r="M294" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="295" spans="1:13">
@@ -14810,11 +14811,11 @@
       <c r="K295" s="10">
         <v>4.9887445887445897E-2</v>
       </c>
-      <c r="L295" s="9" t="s">
+      <c r="L295" s="10">
+        <v>0.25974025974025972</v>
+      </c>
+      <c r="M295" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M295" s="10">
-        <v>0.25974025974025972</v>
       </c>
     </row>
     <row r="296" spans="1:13">
@@ -14851,11 +14852,11 @@
       <c r="K296" s="10">
         <v>4.6536796536796543E-2</v>
       </c>
-      <c r="L296" s="9" t="s">
+      <c r="L296" s="10">
+        <v>0.25974025974025972</v>
+      </c>
+      <c r="M296" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M296" s="10">
-        <v>0.25974025974025972</v>
       </c>
     </row>
     <row r="297" spans="1:13">
@@ -14892,11 +14893,11 @@
       <c r="K297" s="10">
         <v>8.0701754385964913E-2</v>
       </c>
-      <c r="L297" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M297" s="10">
-        <v>0</v>
+      <c r="L297" s="10">
+        <v>0</v>
+      </c>
+      <c r="M297" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="298" spans="1:13">
@@ -14933,11 +14934,11 @@
       <c r="K298" s="10">
         <v>7.6243093922651939E-2</v>
       </c>
-      <c r="L298" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M298" s="10">
-        <v>0</v>
+      <c r="L298" s="10">
+        <v>0</v>
+      </c>
+      <c r="M298" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="299" spans="1:13">
@@ -14974,11 +14975,11 @@
       <c r="K299" s="10">
         <v>8.1898865263314913E-2</v>
       </c>
-      <c r="L299" s="9" t="s">
+      <c r="L299" s="10">
+        <v>0.2373300370828183</v>
+      </c>
+      <c r="M299" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M299" s="10">
-        <v>0.2373300370828183</v>
       </c>
     </row>
     <row r="300" spans="1:13">
@@ -15015,11 +15016,11 @@
       <c r="K300" s="10">
         <v>8.389057750759879E-2</v>
       </c>
-      <c r="L300" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M300" s="10">
-        <v>0</v>
+      <c r="L300" s="10">
+        <v>0</v>
+      </c>
+      <c r="M300" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="301" spans="1:13">
@@ -15056,11 +15057,11 @@
       <c r="K301" s="10">
         <v>6.9565731572798578E-2</v>
       </c>
-      <c r="L301" s="9" t="s">
+      <c r="L301" s="10">
+        <v>0.36390225492971034</v>
+      </c>
+      <c r="M301" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M301" s="10">
-        <v>0.36390225492971034</v>
       </c>
     </row>
     <row r="302" spans="1:13">
@@ -15097,11 +15098,11 @@
       <c r="K302" s="10">
         <v>7.7334287122874518E-2</v>
       </c>
-      <c r="L302" s="9" t="s">
+      <c r="L302" s="10">
+        <v>0.36892321671967288</v>
+      </c>
+      <c r="M302" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M302" s="10">
-        <v>0.36892321671967288</v>
       </c>
     </row>
     <row r="303" spans="1:13">
@@ -15138,11 +15139,11 @@
       <c r="K303" s="10">
         <v>0.10147058823529413</v>
       </c>
-      <c r="L303" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M303" s="10">
-        <v>0</v>
+      <c r="L303" s="10">
+        <v>0</v>
+      </c>
+      <c r="M303" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="304" spans="1:13">
@@ -15179,11 +15180,11 @@
       <c r="K304" s="10">
         <v>0</v>
       </c>
-      <c r="L304" s="9" t="s">
+      <c r="L304" s="10">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="M304" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M304" s="10">
-        <v>0.27777777777777779</v>
       </c>
     </row>
     <row r="305" spans="1:13">
@@ -15220,11 +15221,11 @@
       <c r="K305" s="10">
         <v>0</v>
       </c>
-      <c r="L305" s="9" t="s">
+      <c r="L305" s="10">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="M305" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M305" s="10">
-        <v>0.27777777777777779</v>
       </c>
     </row>
     <row r="306" spans="1:13" s="4" customFormat="1">
@@ -15261,11 +15262,11 @@
       <c r="K306" s="10">
         <v>9.9999883536213238E-2</v>
       </c>
-      <c r="L306" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M306" s="10">
-        <v>0</v>
+      <c r="L306" s="10">
+        <v>0</v>
+      </c>
+      <c r="M306" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="307" spans="1:13">
@@ -15302,11 +15303,11 @@
       <c r="K307" s="10">
         <v>0.19980525310773045</v>
       </c>
-      <c r="L307" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M307" s="10">
-        <v>0</v>
+      <c r="L307" s="10">
+        <v>0</v>
+      </c>
+      <c r="M307" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="308" spans="1:13">
@@ -15343,11 +15344,11 @@
       <c r="K308" s="10">
         <v>0.39992049294374876</v>
       </c>
-      <c r="L308" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M308" s="10">
-        <v>0</v>
+      <c r="L308" s="10">
+        <v>0</v>
+      </c>
+      <c r="M308" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="309" spans="1:13">
@@ -15384,11 +15385,11 @@
       <c r="K309" s="10">
         <v>0.40026346455895012</v>
       </c>
-      <c r="L309" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M309" s="10">
-        <v>0</v>
+      <c r="L309" s="10">
+        <v>0</v>
+      </c>
+      <c r="M309" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="310" spans="1:13">
@@ -15425,11 +15426,11 @@
       <c r="K310" s="10">
         <v>5.1094890510948905E-2</v>
       </c>
-      <c r="L310" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M310" s="10">
-        <v>0</v>
+      <c r="L310" s="10">
+        <v>0</v>
+      </c>
+      <c r="M310" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="311" spans="1:13">
@@ -15466,11 +15467,11 @@
       <c r="K311" s="10">
         <v>0.10218978102189781</v>
       </c>
-      <c r="L311" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M311" s="10">
-        <v>0</v>
+      <c r="L311" s="10">
+        <v>0</v>
+      </c>
+      <c r="M311" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="312" spans="1:13">
@@ -15507,11 +15508,11 @@
       <c r="K312" s="10">
         <v>3.8321167883211681E-2</v>
       </c>
-      <c r="L312" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M312" s="10">
-        <v>0</v>
+      <c r="L312" s="10">
+        <v>0</v>
+      </c>
+      <c r="M312" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="313" spans="1:13">
@@ -15548,11 +15549,11 @@
       <c r="K313" s="10">
         <v>7.6642335766423361E-2</v>
       </c>
-      <c r="L313" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M313" s="10">
-        <v>0</v>
+      <c r="L313" s="10">
+        <v>0</v>
+      </c>
+      <c r="M313" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="314" spans="1:13">
@@ -15589,11 +15590,11 @@
       <c r="K314" s="10">
         <v>5.1094890510948905E-2</v>
       </c>
-      <c r="L314" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M314" s="10">
-        <v>0</v>
+      <c r="L314" s="10">
+        <v>0</v>
+      </c>
+      <c r="M314" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="315" spans="1:13">
@@ -15630,11 +15631,11 @@
       <c r="K315" s="10">
         <v>0.10218978102189781</v>
       </c>
-      <c r="L315" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M315" s="10">
-        <v>0</v>
+      <c r="L315" s="10">
+        <v>0</v>
+      </c>
+      <c r="M315" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="316" spans="1:13">
@@ -15671,11 +15672,11 @@
       <c r="K316" s="10">
         <v>5.1094890510948905E-2</v>
       </c>
-      <c r="L316" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M316" s="10">
-        <v>0</v>
+      <c r="L316" s="10">
+        <v>0</v>
+      </c>
+      <c r="M316" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="317" spans="1:13">
@@ -15712,11 +15713,11 @@
       <c r="K317" s="10">
         <v>0.10218978102189781</v>
       </c>
-      <c r="L317" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M317" s="10">
-        <v>0</v>
+      <c r="L317" s="10">
+        <v>0</v>
+      </c>
+      <c r="M317" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="318" spans="1:13">
@@ -15753,11 +15754,11 @@
       <c r="K318" s="10">
         <v>5.1094890510948905E-2</v>
       </c>
-      <c r="L318" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M318" s="10">
-        <v>0</v>
+      <c r="L318" s="10">
+        <v>0</v>
+      </c>
+      <c r="M318" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="319" spans="1:13">
@@ -15794,11 +15795,11 @@
       <c r="K319" s="10">
         <v>0.10218978102189781</v>
       </c>
-      <c r="L319" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M319" s="10">
-        <v>0</v>
+      <c r="L319" s="10">
+        <v>0</v>
+      </c>
+      <c r="M319" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="320" spans="1:13">
@@ -15835,11 +15836,11 @@
       <c r="K320" s="10">
         <v>4.9999690183782981E-2</v>
       </c>
-      <c r="L320" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M320" s="10">
-        <v>0</v>
+      <c r="L320" s="10">
+        <v>0</v>
+      </c>
+      <c r="M320" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="321" spans="1:13">
@@ -15876,11 +15877,11 @@
       <c r="K321" s="10">
         <v>0.24962649402390438</v>
       </c>
-      <c r="L321" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M321" s="10">
-        <v>0</v>
+      <c r="L321" s="10">
+        <v>0</v>
+      </c>
+      <c r="M321" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="322" spans="1:13">
@@ -15917,11 +15918,11 @@
       <c r="K322" s="10">
         <v>0.49940191387559812</v>
       </c>
-      <c r="L322" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M322" s="10">
-        <v>0</v>
+      <c r="L322" s="10">
+        <v>0</v>
+      </c>
+      <c r="M322" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="323" spans="1:13">
@@ -15958,11 +15959,11 @@
       <c r="K323" s="10">
         <v>0.48659673659673658</v>
       </c>
-      <c r="L323" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M323" s="10">
-        <v>0</v>
+      <c r="L323" s="10">
+        <v>0</v>
+      </c>
+      <c r="M323" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="324" spans="1:13">
@@ -15999,11 +16000,11 @@
       <c r="K324" s="10">
         <v>0.10335917312661498</v>
       </c>
-      <c r="L324" s="9" t="s">
+      <c r="L324" s="10">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="M324" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M324" s="10">
-        <v>0.27777777777777779</v>
       </c>
     </row>
     <row r="325" spans="1:13">
@@ -16040,11 +16041,11 @@
       <c r="K325" s="10">
         <v>0.11240310077519379</v>
       </c>
-      <c r="L325" s="9" t="s">
+      <c r="L325" s="10">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="M325" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M325" s="10">
-        <v>0.27777777777777779</v>
       </c>
     </row>
     <row r="326" spans="1:13">
@@ -16081,11 +16082,11 @@
       <c r="K326" s="10">
         <v>9.2592592592592587E-2</v>
       </c>
-      <c r="L326" s="9" t="s">
+      <c r="L326" s="10">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="M326" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M326" s="10">
-        <v>0.27777777777777779</v>
       </c>
     </row>
     <row r="327" spans="1:13">
@@ -16122,11 +16123,11 @@
       <c r="K327" s="10">
         <v>0</v>
       </c>
-      <c r="L327" s="9" t="s">
+      <c r="L327" s="10">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="M327" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M327" s="10">
-        <v>0.27777777777777779</v>
       </c>
     </row>
     <row r="328" spans="1:13">
@@ -16163,11 +16164,11 @@
       <c r="K328" s="10">
         <v>0.107095046854083</v>
       </c>
-      <c r="L328" s="9" t="s">
+      <c r="L328" s="10">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="M328" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M328" s="10">
-        <v>0.27777777777777779</v>
       </c>
     </row>
     <row r="329" spans="1:13">
@@ -16204,11 +16205,11 @@
       <c r="K329" s="10">
         <v>0.107095046854083</v>
       </c>
-      <c r="L329" s="9" t="s">
+      <c r="L329" s="10">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="M329" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M329" s="10">
-        <v>0.27777777777777779</v>
       </c>
     </row>
     <row r="330" spans="1:13">
@@ -16245,11 +16246,11 @@
       <c r="K330" s="10">
         <v>5.5741360089186183E-2</v>
       </c>
-      <c r="L330" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M330" s="10">
-        <v>0</v>
+      <c r="L330" s="10">
+        <v>0</v>
+      </c>
+      <c r="M330" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="331" spans="1:13">
@@ -16286,11 +16287,11 @@
       <c r="K331" s="10">
         <v>4.800691299547135E-2</v>
       </c>
-      <c r="L331" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M331" s="10">
-        <v>0</v>
+      <c r="L331" s="10">
+        <v>0</v>
+      </c>
+      <c r="M331" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="332" spans="1:13">
@@ -16327,11 +16328,11 @@
       <c r="K332" s="10">
         <v>0</v>
       </c>
-      <c r="L332" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M332" s="10">
-        <v>0</v>
+      <c r="L332" s="10">
+        <v>0</v>
+      </c>
+      <c r="M332" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="333" spans="1:13">
@@ -16368,11 +16369,11 @@
       <c r="K333" s="10">
         <v>0</v>
       </c>
-      <c r="L333" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M333" s="10">
-        <v>0</v>
+      <c r="L333" s="10">
+        <v>0</v>
+      </c>
+      <c r="M333" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="334" spans="1:13">
@@ -16409,11 +16410,11 @@
       <c r="K334" s="10">
         <v>5.0774308200050779E-2</v>
       </c>
-      <c r="L334" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M334" s="10">
-        <v>0</v>
+      <c r="L334" s="10">
+        <v>0</v>
+      </c>
+      <c r="M334" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="335" spans="1:13">
@@ -16450,11 +16451,11 @@
       <c r="K335" s="10">
         <v>5.1986760704940474E-2</v>
       </c>
-      <c r="L335" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M335" s="10">
-        <v>0</v>
+      <c r="L335" s="10">
+        <v>0</v>
+      </c>
+      <c r="M335" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="336" spans="1:13">
@@ -16491,11 +16492,11 @@
       <c r="K336" s="10">
         <v>0</v>
       </c>
-      <c r="L336" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M336" s="10">
-        <v>0</v>
+      <c r="L336" s="10">
+        <v>0</v>
+      </c>
+      <c r="M336" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="337" spans="1:13">
@@ -16532,11 +16533,11 @@
       <c r="K337" s="10">
         <v>0</v>
       </c>
-      <c r="L337" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M337" s="10">
-        <v>0</v>
+      <c r="L337" s="10">
+        <v>0</v>
+      </c>
+      <c r="M337" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="338" spans="1:13">
@@ -16573,11 +16574,11 @@
       <c r="K338" s="10">
         <v>0.1</v>
       </c>
-      <c r="L338" s="9" t="s">
+      <c r="L338" s="10">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="M338" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M338" s="10">
-        <v>0.27777777777777779</v>
       </c>
     </row>
     <row r="339" spans="1:13">
@@ -16614,11 +16615,11 @@
       <c r="K339" s="10">
         <v>0.2</v>
       </c>
-      <c r="L339" s="9" t="s">
+      <c r="L339" s="10">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="M339" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M339" s="10">
-        <v>0.27777777777777779</v>
       </c>
     </row>
     <row r="340" spans="1:13">
@@ -16655,11 +16656,11 @@
       <c r="K340" s="10">
         <v>0.3</v>
       </c>
-      <c r="L340" s="9" t="s">
+      <c r="L340" s="10">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="M340" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M340" s="10">
-        <v>0.27777777777777779</v>
       </c>
     </row>
     <row r="341" spans="1:13">
@@ -16696,11 +16697,11 @@
       <c r="K341" s="10">
         <v>0.3</v>
       </c>
-      <c r="L341" s="9" t="s">
+      <c r="L341" s="10">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="M341" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M341" s="10">
-        <v>0.27777777777777779</v>
       </c>
     </row>
     <row r="342" spans="1:13">
@@ -16737,11 +16738,11 @@
       <c r="K342" s="10">
         <v>0.3</v>
       </c>
-      <c r="L342" s="9" t="s">
+      <c r="L342" s="10">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="M342" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M342" s="10">
-        <v>0.27777777777777779</v>
       </c>
     </row>
     <row r="343" spans="1:13">
@@ -16778,11 +16779,11 @@
       <c r="K343" s="10">
         <v>0.3</v>
       </c>
-      <c r="L343" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M343" s="10">
-        <v>0</v>
+      <c r="L343" s="10">
+        <v>0</v>
+      </c>
+      <c r="M343" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="344" spans="1:13">
@@ -16819,11 +16820,11 @@
       <c r="K344" s="10">
         <v>0</v>
       </c>
-      <c r="L344" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M344" s="10">
-        <v>0</v>
+      <c r="L344" s="10">
+        <v>0</v>
+      </c>
+      <c r="M344" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="345" spans="1:13">
@@ -16860,11 +16861,11 @@
       <c r="K345" s="10">
         <v>0</v>
       </c>
-      <c r="L345" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M345" s="10">
-        <v>0</v>
+      <c r="L345" s="10">
+        <v>0</v>
+      </c>
+      <c r="M345" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="346" spans="1:13">
@@ -16901,11 +16902,11 @@
       <c r="K346" s="10">
         <v>0</v>
       </c>
-      <c r="L346" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M346" s="10">
-        <v>0</v>
+      <c r="L346" s="10">
+        <v>0</v>
+      </c>
+      <c r="M346" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="347" spans="1:13">
@@ -16942,11 +16943,11 @@
       <c r="K347" s="10">
         <v>0</v>
       </c>
-      <c r="L347" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M347" s="10">
-        <v>0</v>
+      <c r="L347" s="10">
+        <v>0</v>
+      </c>
+      <c r="M347" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="348" spans="1:13">
@@ -16983,11 +16984,11 @@
       <c r="K348" s="10">
         <v>0</v>
       </c>
-      <c r="L348" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M348" s="10">
-        <v>0</v>
+      <c r="L348" s="10">
+        <v>0</v>
+      </c>
+      <c r="M348" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="349" spans="1:13">
@@ -17024,11 +17025,11 @@
       <c r="K349" s="10">
         <v>0</v>
       </c>
-      <c r="L349" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M349" s="10">
-        <v>0</v>
+      <c r="L349" s="10">
+        <v>0</v>
+      </c>
+      <c r="M349" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="350" spans="1:13">
@@ -17065,11 +17066,11 @@
       <c r="K350" s="10">
         <v>0</v>
       </c>
-      <c r="L350" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M350" s="10">
-        <v>0</v>
+      <c r="L350" s="10">
+        <v>0</v>
+      </c>
+      <c r="M350" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="351" spans="1:13">
@@ -17106,11 +17107,11 @@
       <c r="K351" s="10">
         <v>0</v>
       </c>
-      <c r="L351" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M351" s="10">
-        <v>0</v>
+      <c r="L351" s="10">
+        <v>0</v>
+      </c>
+      <c r="M351" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="352" spans="1:13">
@@ -17147,11 +17148,11 @@
       <c r="K352" s="10">
         <v>0</v>
       </c>
-      <c r="L352" s="9" t="s">
+      <c r="L352" s="10">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="M352" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M352" s="10">
-        <v>0.27777777777777779</v>
       </c>
     </row>
     <row r="353" spans="1:13">
@@ -17188,11 +17189,11 @@
       <c r="K353" s="10">
         <v>5.6980056980056981E-2</v>
       </c>
-      <c r="L353" s="9" t="s">
+      <c r="L353" s="10">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="M353" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M353" s="10">
-        <v>0.27777777777777779</v>
       </c>
     </row>
     <row r="354" spans="1:13">
@@ -17229,11 +17230,11 @@
       <c r="K354" s="10">
         <v>0.13995562382659157</v>
       </c>
-      <c r="L354" s="9" t="s">
+      <c r="L354" s="10">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="M354" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M354" s="10">
-        <v>0.27777777777777779</v>
       </c>
     </row>
     <row r="355" spans="1:13">
@@ -17270,11 +17271,11 @@
       <c r="K355" s="10">
         <v>0</v>
       </c>
-      <c r="L355" s="9" t="s">
+      <c r="L355" s="10">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="M355" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M355" s="10">
-        <v>0.27777777777777779</v>
       </c>
     </row>
     <row r="356" spans="1:13">
@@ -17311,11 +17312,11 @@
       <c r="K356" s="10">
         <v>6.0086682427107956E-2</v>
       </c>
-      <c r="L356" s="9" t="s">
+      <c r="L356" s="10">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="M356" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M356" s="10">
-        <v>0.27777777777777779</v>
       </c>
     </row>
     <row r="357" spans="1:13">
@@ -17352,11 +17353,11 @@
       <c r="K357" s="10">
         <v>0.12463900288797691</v>
       </c>
-      <c r="L357" s="9" t="s">
+      <c r="L357" s="10">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="M357" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M357" s="10">
-        <v>0.27777777777777779</v>
       </c>
     </row>
     <row r="358" spans="1:13">
@@ -17393,11 +17394,11 @@
       <c r="K358" s="10">
         <v>6.4092461255581823E-2</v>
       </c>
-      <c r="L358" s="9" t="s">
+      <c r="L358" s="10">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="M358" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M358" s="10">
-        <v>0.27777777777777779</v>
       </c>
     </row>
     <row r="359" spans="1:13">
@@ -17434,11 +17435,11 @@
       <c r="K359" s="10">
         <v>3.2251352476071575E-2</v>
       </c>
-      <c r="L359" s="9" t="s">
+      <c r="L359" s="10">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="M359" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="M359" s="10">
-        <v>0.27777777777777779</v>
       </c>
     </row>
     <row r="360" spans="1:13">
@@ -17475,11 +17476,11 @@
       <c r="K360" s="10">
         <v>0.129953022875817</v>
       </c>
-      <c r="L360" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M360" s="10">
-        <v>0</v>
+      <c r="L360" s="10">
+        <v>0</v>
+      </c>
+      <c r="M360" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="361" spans="1:13">
@@ -17516,11 +17517,11 @@
       <c r="K361" s="10">
         <v>0.129953022875817</v>
       </c>
-      <c r="L361" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M361" s="10">
-        <v>0</v>
+      <c r="L361" s="10">
+        <v>0</v>
+      </c>
+      <c r="M361" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="362" spans="1:13">
@@ -17557,11 +17558,11 @@
       <c r="K362" s="10">
         <v>0</v>
       </c>
-      <c r="L362" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M362" s="10">
-        <v>0</v>
+      <c r="L362" s="10">
+        <v>0</v>
+      </c>
+      <c r="M362" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="363" spans="1:13">
@@ -17598,11 +17599,11 @@
       <c r="K363" s="10">
         <v>0</v>
       </c>
-      <c r="L363" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M363" s="10">
-        <v>0</v>
+      <c r="L363" s="10">
+        <v>0</v>
+      </c>
+      <c r="M363" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="364" spans="1:13">
@@ -17639,11 +17640,11 @@
       <c r="K364" s="10">
         <v>0</v>
       </c>
-      <c r="L364" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M364" s="10">
-        <v>0</v>
+      <c r="L364" s="10">
+        <v>0</v>
+      </c>
+      <c r="M364" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="365" spans="1:13">
@@ -17680,11 +17681,11 @@
       <c r="K365" s="10">
         <v>9.8765432098765427E-2</v>
       </c>
-      <c r="L365" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M365" s="10">
-        <v>0</v>
+      <c r="L365" s="10">
+        <v>0</v>
+      </c>
+      <c r="M365" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="366" spans="1:13">
@@ -17721,11 +17722,11 @@
       <c r="K366" s="10">
         <v>0</v>
       </c>
-      <c r="L366" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M366" s="10">
-        <v>0</v>
+      <c r="L366" s="10">
+        <v>0</v>
+      </c>
+      <c r="M366" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="367" spans="1:13">
@@ -17762,11 +17763,11 @@
       <c r="K367" s="10">
         <v>0</v>
       </c>
-      <c r="L367" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M367" s="10">
-        <v>0</v>
+      <c r="L367" s="10">
+        <v>0</v>
+      </c>
+      <c r="M367" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="368" spans="1:13">
@@ -17803,11 +17804,11 @@
       <c r="K368" s="10">
         <v>0</v>
       </c>
-      <c r="L368" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M368" s="10">
-        <v>0</v>
+      <c r="L368" s="10">
+        <v>0</v>
+      </c>
+      <c r="M368" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="369" spans="1:13">
@@ -17844,11 +17845,11 @@
       <c r="K369" s="10">
         <v>0</v>
       </c>
-      <c r="L369" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M369" s="10">
-        <v>0</v>
+      <c r="L369" s="10">
+        <v>0</v>
+      </c>
+      <c r="M369" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="370" spans="1:13">
@@ -17885,11 +17886,11 @@
       <c r="K370" s="10">
         <v>0</v>
       </c>
-      <c r="L370" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M370" s="10">
-        <v>0</v>
+      <c r="L370" s="10">
+        <v>0</v>
+      </c>
+      <c r="M370" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="371" spans="1:13">
@@ -17926,11 +17927,11 @@
       <c r="K371" s="10">
         <v>0</v>
       </c>
-      <c r="L371" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M371" s="10">
-        <v>0</v>
+      <c r="L371" s="10">
+        <v>0</v>
+      </c>
+      <c r="M371" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="372" spans="1:13">
@@ -17967,11 +17968,11 @@
       <c r="K372" s="10">
         <v>0.18005157191452692</v>
       </c>
-      <c r="L372" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M372" s="10">
-        <v>0</v>
+      <c r="L372" s="10">
+        <v>0</v>
+      </c>
+      <c r="M372" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="373" spans="1:13">
@@ -18008,11 +18009,11 @@
       <c r="K373" s="10">
         <v>2.360271903323263E-2</v>
       </c>
-      <c r="L373" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M373" s="10">
-        <v>0</v>
+      <c r="L373" s="10">
+        <v>0</v>
+      </c>
+      <c r="M373" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="374" spans="1:13">
@@ -18049,11 +18050,11 @@
       <c r="K374" s="10">
         <v>8.6142917726887189E-2</v>
       </c>
-      <c r="L374" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M374" s="10">
-        <v>0</v>
+      <c r="L374" s="10">
+        <v>0</v>
+      </c>
+      <c r="M374" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="375" spans="1:13">
@@ -18090,11 +18091,11 @@
       <c r="K375" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="L375" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M375" s="10">
-        <v>0</v>
+      <c r="L375" s="10">
+        <v>0</v>
+      </c>
+      <c r="M375" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="376" spans="1:13">
@@ -18131,11 +18132,11 @@
       <c r="K376" s="10">
         <v>0</v>
       </c>
-      <c r="L376" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M376" s="10">
-        <v>0</v>
+      <c r="L376" s="10">
+        <v>0</v>
+      </c>
+      <c r="M376" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="377" spans="1:13">
@@ -18172,11 +18173,11 @@
       <c r="K377" s="10">
         <v>0</v>
       </c>
-      <c r="L377" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M377" s="10">
-        <v>0</v>
+      <c r="L377" s="10">
+        <v>0</v>
+      </c>
+      <c r="M377" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="378" spans="1:13">
@@ -18213,11 +18214,11 @@
       <c r="K378" s="10">
         <v>0</v>
       </c>
-      <c r="L378" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M378" s="10">
-        <v>0</v>
+      <c r="L378" s="10">
+        <v>0</v>
+      </c>
+      <c r="M378" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="379" spans="1:13">
@@ -18254,11 +18255,11 @@
       <c r="K379" s="10">
         <v>0</v>
       </c>
-      <c r="L379" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M379" s="10">
-        <v>0</v>
+      <c r="L379" s="10">
+        <v>0</v>
+      </c>
+      <c r="M379" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="380" spans="1:13">
@@ -18295,11 +18296,11 @@
       <c r="K380" s="10">
         <v>0</v>
       </c>
-      <c r="L380" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M380" s="10">
-        <v>0</v>
+      <c r="L380" s="10">
+        <v>0</v>
+      </c>
+      <c r="M380" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="381" spans="1:13">
@@ -18336,11 +18337,11 @@
       <c r="K381" s="10">
         <v>0</v>
       </c>
-      <c r="L381" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M381" s="10">
-        <v>0</v>
+      <c r="L381" s="10">
+        <v>0</v>
+      </c>
+      <c r="M381" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="382" spans="1:13">
@@ -18377,11 +18378,11 @@
       <c r="K382" s="10">
         <v>0</v>
       </c>
-      <c r="L382" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M382" s="10">
-        <v>0</v>
+      <c r="L382" s="10">
+        <v>0</v>
+      </c>
+      <c r="M382" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="383" spans="1:13">
@@ -18418,11 +18419,11 @@
       <c r="K383" s="10">
         <v>7.8641971203405048E-2</v>
       </c>
-      <c r="L383" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M383" s="10">
-        <v>0</v>
+      <c r="L383" s="10">
+        <v>0</v>
+      </c>
+      <c r="M383" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="384" spans="1:13">
@@ -18459,11 +18460,11 @@
       <c r="K384" s="10">
         <v>0</v>
       </c>
-      <c r="L384" s="9" t="s">
+      <c r="L384" s="10">
+        <v>0.22727272727272727</v>
+      </c>
+      <c r="M384" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M384" s="10">
-        <v>0.22727272727272727</v>
       </c>
     </row>
     <row r="385" spans="1:13">
@@ -18500,11 +18501,11 @@
       <c r="K385" s="10">
         <v>0</v>
       </c>
-      <c r="L385" s="9" t="s">
+      <c r="L385" s="10">
+        <v>0.22727272727272727</v>
+      </c>
+      <c r="M385" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M385" s="10">
-        <v>0.22727272727272727</v>
       </c>
     </row>
     <row r="386" spans="1:13">
@@ -18541,11 +18542,11 @@
       <c r="K386" s="10">
         <v>0</v>
       </c>
-      <c r="L386" s="9" t="s">
+      <c r="L386" s="10">
+        <v>0.22727272727272727</v>
+      </c>
+      <c r="M386" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="M386" s="10">
-        <v>0.22727272727272727</v>
       </c>
     </row>
     <row r="387" spans="1:13">
@@ -18582,11 +18583,11 @@
       <c r="K387" s="10">
         <v>3.5868893011750155E-2</v>
       </c>
-      <c r="L387" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M387" s="10">
-        <v>0</v>
+      <c r="L387" s="10">
+        <v>0</v>
+      </c>
+      <c r="M387" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="388" spans="1:13">
@@ -18623,11 +18624,11 @@
       <c r="K388" s="10">
         <v>4.0027605244996552E-2</v>
       </c>
-      <c r="L388" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M388" s="10">
-        <v>0</v>
+      <c r="L388" s="10">
+        <v>0</v>
+      </c>
+      <c r="M388" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="389" spans="1:13">
@@ -18664,11 +18665,11 @@
       <c r="K389" s="10">
         <v>3.8147855827413833E-2</v>
       </c>
-      <c r="L389" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M389" s="10">
-        <v>0</v>
+      <c r="L389" s="10">
+        <v>0</v>
+      </c>
+      <c r="M389" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="390" spans="1:13">
@@ -18705,11 +18706,11 @@
       <c r="K390" s="10">
         <v>0</v>
       </c>
-      <c r="L390" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M390" s="10">
-        <v>0</v>
+      <c r="L390" s="10">
+        <v>0</v>
+      </c>
+      <c r="M390" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="391" spans="1:13">
@@ -18746,11 +18747,11 @@
       <c r="K391" s="10">
         <v>7.4656981436642456E-2</v>
       </c>
-      <c r="L391" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M391" s="10">
-        <v>0</v>
+      <c r="L391" s="10">
+        <v>0</v>
+      </c>
+      <c r="M391" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="392" spans="1:13">
@@ -18787,11 +18788,11 @@
       <c r="K392" s="10">
         <v>3.7022852036256867E-2</v>
       </c>
-      <c r="L392" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M392" s="10">
-        <v>0</v>
+      <c r="L392" s="10">
+        <v>0</v>
+      </c>
+      <c r="M392" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="393" spans="1:13">
@@ -18828,11 +18829,11 @@
       <c r="K393" s="10">
         <v>5.5E-2</v>
       </c>
-      <c r="L393" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M393" s="10">
-        <v>0</v>
+      <c r="L393" s="10">
+        <v>0</v>
+      </c>
+      <c r="M393" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="394" spans="1:13" ht="13.5" customHeight="1">
@@ -18869,11 +18870,11 @@
       <c r="K394" s="10">
         <v>5.5E-2</v>
       </c>
-      <c r="L394" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M394" s="10">
-        <v>0</v>
+      <c r="L394" s="10">
+        <v>0</v>
+      </c>
+      <c r="M394" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -18884,13 +18885,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00991B6C-43A6-4EB2-8C9D-9A614BDDB87B}">
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="19.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.5">
@@ -18905,31 +18906,31 @@
         <v>399</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="J1" s="7" t="s">
         <v>448</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>454</v>
-      </c>
       <c r="K1" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="L1" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="M1" s="6" t="s">
         <v>281</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -18966,11 +18967,11 @@
       <c r="K2" s="13">
         <v>0.3</v>
       </c>
-      <c r="L2" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="M2" s="13">
-        <v>0</v>
+      <c r="L2" s="13">
+        <v>0</v>
+      </c>
+      <c r="M2" s="15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -19007,11 +19008,11 @@
       <c r="K3" s="13">
         <v>0</v>
       </c>
-      <c r="L3" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="M3" s="13">
-        <v>0</v>
+      <c r="L3" s="13">
+        <v>0</v>
+      </c>
+      <c r="M3" s="15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -19048,11 +19049,11 @@
       <c r="K4" s="13">
         <v>0.28000000000000003</v>
       </c>
-      <c r="L4" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="M4" s="13">
-        <v>0</v>
+      <c r="L4" s="13">
+        <v>0</v>
+      </c>
+      <c r="M4" s="15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -19089,11 +19090,11 @@
       <c r="K5" s="13">
         <v>0.24</v>
       </c>
-      <c r="L5" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="M5" s="13">
-        <v>0</v>
+      <c r="L5" s="13">
+        <v>0</v>
+      </c>
+      <c r="M5" s="15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -19130,11 +19131,11 @@
       <c r="K6" s="13">
         <v>0.28000000000000003</v>
       </c>
-      <c r="L6" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="M6" s="13">
-        <v>0</v>
+      <c r="L6" s="13">
+        <v>0</v>
+      </c>
+      <c r="M6" s="15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -19171,11 +19172,11 @@
       <c r="K7" s="13">
         <v>0.2</v>
       </c>
-      <c r="L7" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="M7" s="13">
-        <v>0</v>
+      <c r="L7" s="13">
+        <v>0</v>
+      </c>
+      <c r="M7" s="15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -19212,11 +19213,11 @@
       <c r="K8" s="13">
         <v>0.2</v>
       </c>
-      <c r="L8" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="M8" s="13">
-        <v>0</v>
+      <c r="L8" s="13">
+        <v>0</v>
+      </c>
+      <c r="M8" s="15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -19253,11 +19254,11 @@
       <c r="K9" s="13">
         <v>0.2</v>
       </c>
-      <c r="L9" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="M9" s="13">
-        <v>0</v>
+      <c r="L9" s="13">
+        <v>0</v>
+      </c>
+      <c r="M9" s="15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -19294,11 +19295,11 @@
       <c r="K10" s="13">
         <v>0.2</v>
       </c>
-      <c r="L10" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="M10" s="13">
-        <v>0</v>
+      <c r="L10" s="13">
+        <v>0</v>
+      </c>
+      <c r="M10" s="15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -19335,11 +19336,11 @@
       <c r="K11" s="13">
         <v>0.05</v>
       </c>
-      <c r="L11" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="M11" s="13">
-        <v>0</v>
+      <c r="L11" s="13">
+        <v>0</v>
+      </c>
+      <c r="M11" s="15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -19376,11 +19377,11 @@
       <c r="K12" s="13">
         <v>0.1</v>
       </c>
-      <c r="L12" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="M12" s="13">
-        <v>0</v>
+      <c r="L12" s="13">
+        <v>0</v>
+      </c>
+      <c r="M12" s="15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -19417,11 +19418,11 @@
       <c r="K13" s="13">
         <v>3.1748999999999999E-2</v>
       </c>
-      <c r="L13" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="M13" s="13">
-        <v>0</v>
+      <c r="L13" s="13">
+        <v>0</v>
+      </c>
+      <c r="M13" s="15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -19458,11 +19459,11 @@
       <c r="K14" s="13">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="L14" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="13">
-        <v>0</v>
+      <c r="L14" s="13">
+        <v>0</v>
+      </c>
+      <c r="M14" s="15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -19499,11 +19500,11 @@
       <c r="K15" s="13">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="L15" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="M15" s="13">
-        <v>0</v>
+      <c r="L15" s="13">
+        <v>0</v>
+      </c>
+      <c r="M15" s="15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -19514,7 +19515,7 @@
         <v>432</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="D16" s="2">
         <v>3</v>
@@ -19540,11 +19541,11 @@
       <c r="K16" s="13">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="L16" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="M16" s="13">
-        <v>0</v>
+      <c r="L16" s="13">
+        <v>0</v>
+      </c>
+      <c r="M16" s="15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -19555,7 +19556,7 @@
         <v>432</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="D17" s="2">
         <v>3</v>
@@ -19581,11 +19582,11 @@
       <c r="K17" s="13">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="L17" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="M17" s="13">
-        <v>0</v>
+      <c r="L17" s="13">
+        <v>0</v>
+      </c>
+      <c r="M17" s="15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -19596,7 +19597,7 @@
         <v>432</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="D18" s="2">
         <v>3</v>
@@ -19622,11 +19623,11 @@
       <c r="K18" s="13">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="L18" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="M18" s="13">
-        <v>0</v>
+      <c r="L18" s="13">
+        <v>0</v>
+      </c>
+      <c r="M18" s="15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -19637,7 +19638,7 @@
         <v>432</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="D19" s="2">
         <v>3</v>
@@ -19663,11 +19664,11 @@
       <c r="K19" s="13">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="L19" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="M19" s="13">
-        <v>0</v>
+      <c r="L19" s="13">
+        <v>0</v>
+      </c>
+      <c r="M19" s="15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -19678,7 +19679,7 @@
         <v>432</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="D20" s="2">
         <v>3</v>
@@ -19704,11 +19705,11 @@
       <c r="K20" s="13">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="L20" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="M20" s="13">
-        <v>0</v>
+      <c r="L20" s="13">
+        <v>0</v>
+      </c>
+      <c r="M20" s="15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -19745,11 +19746,11 @@
       <c r="K21" s="13">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="L21" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="M21" s="13">
-        <v>0</v>
+      <c r="L21" s="13">
+        <v>0</v>
+      </c>
+      <c r="M21" s="15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -19760,37 +19761,37 @@
         <v>432</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="D22" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22" s="2">
-        <v>2.1669999999999998</v>
+        <v>0.66</v>
       </c>
       <c r="F22" s="2">
         <v>7.5</v>
       </c>
       <c r="G22" s="2">
-        <v>0.13322834645669293</v>
+        <v>9.6950672645739908E-2</v>
       </c>
       <c r="H22" s="2">
-        <v>0.1146981627296588</v>
+        <v>9.8004484304932749E-2</v>
       </c>
       <c r="I22" s="2">
-        <v>1.7195615748031494</v>
+        <v>1.3239215246636773</v>
       </c>
       <c r="J22" s="13">
         <v>0</v>
       </c>
-      <c r="K22" s="2">
+      <c r="K22" s="13">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="L22" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="M22" s="2">
-        <v>0</v>
+      <c r="L22" s="13">
+        <v>0</v>
+      </c>
+      <c r="M22" s="15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -19801,37 +19802,37 @@
         <v>432</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="D23" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E23" s="2">
-        <v>2.1669999999999998</v>
+        <v>0.66</v>
       </c>
       <c r="F23" s="2">
         <v>7.5</v>
       </c>
       <c r="G23" s="2">
-        <v>0.12540326975476837</v>
+        <v>0.10343850267379678</v>
       </c>
       <c r="H23" s="2">
-        <v>0.12261580381471389</v>
+        <v>0.1212727272727273</v>
       </c>
       <c r="I23" s="2">
-        <v>1.785157929155313</v>
+        <v>1.578794117647059</v>
       </c>
       <c r="J23" s="13">
         <v>0</v>
       </c>
-      <c r="K23" s="2">
+      <c r="K23" s="13">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="L23" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="M23" s="2">
-        <v>0</v>
+      <c r="L23" s="13">
+        <v>0</v>
+      </c>
+      <c r="M23" s="15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -19842,7 +19843,7 @@
         <v>432</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="D24" s="2">
         <v>2</v>
@@ -19850,29 +19851,29 @@
       <c r="E24" s="2">
         <v>2.1669999999999998</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F24" s="13">
         <v>7.5</v>
       </c>
-      <c r="G24" s="2">
-        <v>0.11937958115183248</v>
-      </c>
-      <c r="H24" s="2">
-        <v>0.11806282722513088</v>
-      </c>
-      <c r="I24" s="2">
-        <v>1.7150601047120415</v>
+      <c r="G24" s="16">
+        <v>0.14164383561643837</v>
+      </c>
+      <c r="H24" s="16">
+        <v>0.11975342465753425</v>
+      </c>
+      <c r="I24" s="16">
+        <v>2.1552739726027399</v>
       </c>
       <c r="J24" s="13">
         <v>0</v>
       </c>
-      <c r="K24" s="2">
+      <c r="K24" s="13">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="L24" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="M24" s="2">
-        <v>0</v>
+      <c r="L24" s="13">
+        <v>0</v>
+      </c>
+      <c r="M24" s="15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -19883,7 +19884,7 @@
         <v>432</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="D25" s="2">
         <v>2</v>
@@ -19891,29 +19892,29 @@
       <c r="E25" s="2">
         <v>2.1669999999999998</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F25" s="13">
         <v>7.5</v>
       </c>
-      <c r="G25" s="2">
-        <v>0.15137026819923372</v>
-      </c>
-      <c r="H25" s="2">
-        <v>0.17547892720306513</v>
-      </c>
-      <c r="I25" s="2">
-        <v>2.5101645977011491</v>
+      <c r="G25" s="16">
+        <v>0.10233424657534249</v>
+      </c>
+      <c r="H25" s="16">
+        <v>0.12426301369863016</v>
+      </c>
+      <c r="I25" s="16">
+        <v>2.1552739726027399</v>
       </c>
       <c r="J25" s="13">
         <v>0</v>
       </c>
-      <c r="K25" s="2">
+      <c r="K25" s="13">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="L25" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="M25" s="2">
-        <v>0</v>
+      <c r="L25" s="13">
+        <v>0</v>
+      </c>
+      <c r="M25" s="15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -19921,28 +19922,28 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>455</v>
+        <v>432</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>436</v>
+        <v>465</v>
       </c>
       <c r="D26" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E26" s="2">
-        <v>0.66</v>
-      </c>
-      <c r="F26" s="2">
+        <v>2.1669999999999998</v>
+      </c>
+      <c r="F26" s="13">
         <v>7.5</v>
       </c>
-      <c r="G26" s="2">
-        <v>9.6950672645739908E-2</v>
-      </c>
-      <c r="H26" s="2">
-        <v>9.8004484304932749E-2</v>
-      </c>
-      <c r="I26" s="2">
-        <v>1.3239215246636773</v>
+      <c r="G26" s="16">
+        <v>8.4986301369863015E-2</v>
+      </c>
+      <c r="H26" s="16">
+        <v>5.9232876712328776E-2</v>
+      </c>
+      <c r="I26" s="16">
+        <v>1.6177232876712331</v>
       </c>
       <c r="J26" s="13">
         <v>0</v>
@@ -19950,11 +19951,11 @@
       <c r="K26" s="13">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="L26" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="M26" s="13">
-        <v>0</v>
+      <c r="L26" s="13">
+        <v>0</v>
+      </c>
+      <c r="M26" s="15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -19962,28 +19963,28 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>455</v>
+        <v>432</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>437</v>
+        <v>466</v>
       </c>
       <c r="D27" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E27" s="2">
-        <v>0.66</v>
-      </c>
-      <c r="F27" s="2">
+        <v>2.1669999999999998</v>
+      </c>
+      <c r="F27" s="13">
         <v>7.5</v>
       </c>
-      <c r="G27" s="2">
-        <v>0.10343850267379678</v>
-      </c>
-      <c r="H27" s="2">
-        <v>0.1212727272727273</v>
-      </c>
-      <c r="I27" s="2">
-        <v>1.578794117647059</v>
+      <c r="G27" s="16">
+        <v>7.6750684931506843E-2</v>
+      </c>
+      <c r="H27" s="16">
+        <v>6.213150684931508E-2</v>
+      </c>
+      <c r="I27" s="16">
+        <v>1.6177232876712331</v>
       </c>
       <c r="J27" s="13">
         <v>0</v>
@@ -19991,11 +19992,11 @@
       <c r="K27" s="13">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="L27" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="M27" s="13">
-        <v>0</v>
+      <c r="L27" s="13">
+        <v>0</v>
+      </c>
+      <c r="M27" s="15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -20003,40 +20004,40 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>455</v>
+        <v>432</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="D28" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E28" s="2">
-        <v>0.66</v>
+        <v>2.1669999999999998</v>
       </c>
       <c r="F28" s="2">
         <v>7.5</v>
       </c>
       <c r="G28" s="2">
-        <v>0.11173126614987079</v>
+        <v>0.13322834645669293</v>
       </c>
       <c r="H28" s="2">
-        <v>0.11294573643410853</v>
+        <v>0.1146981627296588</v>
       </c>
       <c r="I28" s="2">
-        <v>0.24167958656330746</v>
+        <v>1.7195615748031494</v>
       </c>
       <c r="J28" s="13">
         <v>0</v>
       </c>
-      <c r="K28" s="13">
+      <c r="K28" s="2">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="L28" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="M28" s="13">
-        <v>0</v>
+      <c r="L28" s="2">
+        <v>0</v>
+      </c>
+      <c r="M28" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -20044,40 +20045,40 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>455</v>
+        <v>432</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="D29" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E29" s="2">
-        <v>0.66</v>
+        <v>2.1669999999999998</v>
       </c>
       <c r="F29" s="2">
         <v>7.5</v>
       </c>
       <c r="G29" s="2">
-        <v>9.9963824289405673E-2</v>
+        <v>0.12540326975476837</v>
       </c>
       <c r="H29" s="2">
-        <v>0.11719896640826874</v>
+        <v>0.12261580381471389</v>
       </c>
       <c r="I29" s="2">
-        <v>0.21888630490956071</v>
+        <v>1.785157929155313</v>
       </c>
       <c r="J29" s="13">
         <v>0</v>
       </c>
-      <c r="K29" s="13">
+      <c r="K29" s="2">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="L29" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="M29" s="13">
-        <v>0</v>
+      <c r="L29" s="2">
+        <v>0</v>
+      </c>
+      <c r="M29" s="18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -20085,166 +20086,424 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>455</v>
+        <v>432</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>438</v>
+        <v>451</v>
       </c>
       <c r="D30" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" s="2">
-        <v>0.66</v>
+        <v>2.1669999999999998</v>
       </c>
       <c r="F30" s="2">
         <v>7.5</v>
       </c>
       <c r="G30" s="2">
-        <v>0.10343850267379678</v>
+        <v>0.11937958115183248</v>
       </c>
       <c r="H30" s="2">
-        <v>0.1212727272727273</v>
+        <v>0.11806282722513088</v>
       </c>
       <c r="I30" s="2">
-        <v>0.22649465240641714</v>
+        <v>1.7150601047120415</v>
       </c>
       <c r="J30" s="13">
-        <v>0.56534491978609624</v>
-      </c>
-      <c r="K30" s="13">
+        <v>0</v>
+      </c>
+      <c r="K30" s="2">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="L30" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="M30" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="15.75" thickBot="1">
+      <c r="L30" s="2">
+        <v>0</v>
+      </c>
+      <c r="M30" s="18" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" s="12">
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>455</v>
+        <v>432</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="D31" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E31" s="2">
-        <v>0.5</v>
+        <v>2.1669999999999998</v>
       </c>
       <c r="F31" s="2">
         <v>7.5</v>
       </c>
       <c r="G31" s="2">
-        <v>0.19780999999999999</v>
+        <v>0.15137026819923372</v>
       </c>
       <c r="H31" s="2">
-        <v>0.20829</v>
+        <v>0.17547892720306513</v>
       </c>
       <c r="I31" s="2">
-        <v>0</v>
+        <v>2.5101645977011491</v>
       </c>
       <c r="J31" s="13">
         <v>0</v>
       </c>
-      <c r="K31" s="13">
-        <v>0</v>
-      </c>
-      <c r="L31" s="17" t="s">
-        <v>416</v>
-      </c>
-      <c r="M31" s="2">
-        <v>0.52173913043478259</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="15.75" thickBot="1">
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="19"/>
-      <c r="J32" s="19"/>
-      <c r="K32" s="19"/>
-      <c r="L32" s="19"/>
-      <c r="M32" s="19"/>
-    </row>
-    <row r="33" spans="2:13">
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="13"/>
-      <c r="K33" s="2"/>
-      <c r="L33" s="2"/>
-      <c r="M33" s="2"/>
-    </row>
-    <row r="34" spans="2:13">
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="13"/>
-      <c r="K34" s="2"/>
-      <c r="L34" s="2"/>
-      <c r="M34" s="2"/>
-    </row>
-    <row r="35" spans="2:13">
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="13"/>
-      <c r="K35" s="2"/>
-      <c r="L35" s="2"/>
-      <c r="M35" s="2"/>
-    </row>
-    <row r="36" spans="2:13">
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="13"/>
-      <c r="K36" s="2"/>
-      <c r="L36" s="2"/>
-      <c r="M36" s="2"/>
-    </row>
-    <row r="37" spans="2:13">
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="13"/>
-      <c r="K37" s="2"/>
-      <c r="L37" s="2"/>
-      <c r="M37" s="2"/>
+      <c r="K31" s="2">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="L31" s="2">
+        <v>0</v>
+      </c>
+      <c r="M31" s="18" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
+      <c r="A32" s="12">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="D32" s="2">
+        <v>3</v>
+      </c>
+      <c r="E32" s="2">
+        <v>1.167</v>
+      </c>
+      <c r="F32" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="G32" s="2">
+        <v>9.9724950884086463E-2</v>
+      </c>
+      <c r="H32" s="2">
+        <v>8.5874263261296671E-2</v>
+      </c>
+      <c r="I32" s="2">
+        <v>0.50931434184675839</v>
+      </c>
+      <c r="J32" s="13">
+        <v>0</v>
+      </c>
+      <c r="K32" s="13">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="L32" s="13">
+        <v>0</v>
+      </c>
+      <c r="M32" s="15" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
+      <c r="A33" s="12">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="D33" s="2">
+        <v>3</v>
+      </c>
+      <c r="E33" s="2">
+        <v>1.167</v>
+      </c>
+      <c r="F33" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="G33" s="2">
+        <v>9.0418467583497045E-2</v>
+      </c>
+      <c r="H33" s="2">
+        <v>8.9108055009823189E-2</v>
+      </c>
+      <c r="I33" s="2">
+        <v>0.50931434184675839</v>
+      </c>
+      <c r="J33" s="13">
+        <v>0</v>
+      </c>
+      <c r="K33" s="13">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="L33" s="13">
+        <v>0</v>
+      </c>
+      <c r="M33" s="15" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
+      <c r="A34" s="12">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D34" s="2">
+        <v>4</v>
+      </c>
+      <c r="E34" s="2">
+        <v>1.167</v>
+      </c>
+      <c r="F34" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="G34" s="2">
+        <v>9.0418467583497045E-2</v>
+      </c>
+      <c r="H34" s="2">
+        <v>8.9108055009823189E-2</v>
+      </c>
+      <c r="I34" s="2">
+        <v>0.50931434184675839</v>
+      </c>
+      <c r="J34" s="13">
+        <v>0.41540078585461687</v>
+      </c>
+      <c r="K34" s="13">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="L34" s="13">
+        <v>0</v>
+      </c>
+      <c r="M34" s="15" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
+      <c r="A35" s="12">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="D35" s="2">
+        <v>3</v>
+      </c>
+      <c r="E35" s="2">
+        <v>1.167</v>
+      </c>
+      <c r="F35" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="G35" s="2">
+        <v>4.79773156899811E-2</v>
+      </c>
+      <c r="H35" s="2">
+        <v>3.5538752362948962E-2</v>
+      </c>
+      <c r="I35" s="2">
+        <v>0.26476370510396979</v>
+      </c>
+      <c r="J35" s="13">
+        <v>0.85026465028355402</v>
+      </c>
+      <c r="K35" s="13">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="L35" s="13">
+        <v>0</v>
+      </c>
+      <c r="M35" s="15" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
+      <c r="A36" s="12">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D36" s="2">
+        <v>3</v>
+      </c>
+      <c r="E36" s="2">
+        <v>1.167</v>
+      </c>
+      <c r="F36" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="G36" s="2">
+        <v>5.0554838709677419E-2</v>
+      </c>
+      <c r="H36" s="2">
+        <v>3.5860215053763439E-2</v>
+      </c>
+      <c r="I36" s="2">
+        <v>0.27945591397849462</v>
+      </c>
+      <c r="J36" s="13">
+        <v>0.76310537634408604</v>
+      </c>
+      <c r="K36" s="13">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="L36" s="13">
+        <v>0</v>
+      </c>
+      <c r="M36" s="15" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
+      <c r="A37" s="12">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="D37" s="2">
+        <v>3</v>
+      </c>
+      <c r="E37" s="2">
+        <v>0.66</v>
+      </c>
+      <c r="F37" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="G37" s="2">
+        <v>0.11173126614987079</v>
+      </c>
+      <c r="H37" s="2">
+        <v>0.11294573643410853</v>
+      </c>
+      <c r="I37" s="2">
+        <v>0.24167958656330746</v>
+      </c>
+      <c r="J37" s="13">
+        <v>0</v>
+      </c>
+      <c r="K37" s="13">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="L37" s="13">
+        <v>0</v>
+      </c>
+      <c r="M37" s="15" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
+      <c r="A38" s="12">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="D38" s="2">
+        <v>3</v>
+      </c>
+      <c r="E38" s="2">
+        <v>0.66</v>
+      </c>
+      <c r="F38" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="G38" s="2">
+        <v>9.9963824289405673E-2</v>
+      </c>
+      <c r="H38" s="2">
+        <v>0.11719896640826874</v>
+      </c>
+      <c r="I38" s="2">
+        <v>0.21888630490956071</v>
+      </c>
+      <c r="J38" s="13">
+        <v>0</v>
+      </c>
+      <c r="K38" s="13">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="L38" s="13">
+        <v>0</v>
+      </c>
+      <c r="M38" s="15" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
+      <c r="A39" s="12">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="D39" s="2">
+        <v>3</v>
+      </c>
+      <c r="E39" s="2">
+        <v>0.66</v>
+      </c>
+      <c r="F39" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="G39" s="2">
+        <v>0.10343850267379678</v>
+      </c>
+      <c r="H39" s="2">
+        <v>0.1212727272727273</v>
+      </c>
+      <c r="I39" s="2">
+        <v>0.22649465240641714</v>
+      </c>
+      <c r="J39" s="13">
+        <v>0</v>
+      </c>
+      <c r="K39" s="13">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="L39" s="13">
+        <v>0</v>
+      </c>
+      <c r="M39" s="15" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13">
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="13"/>
+      <c r="K40" s="13"/>
+      <c r="L40" s="2"/>
+      <c r="M40" s="17"/>
     </row>
   </sheetData>
   <phoneticPr fontId="22" type="noConversion"/>
